--- a/scCO2_Full_Bill_of_Materials.xlsx
+++ b/scCO2_Full_Bill_of_Materials.xlsx
@@ -1126,32 +1126,36 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>442F42</t>
+          <t>SS-RL3S4</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>Parker relief valve, spring-loaded, 1/4" MNPT</t>
+          <t>Swagelok high-pressure relief valve, 1/4" tube compression fitting
+⚠ MUST specify set pressure ~4,350 PSI (30 MPa) when ordering
+⚠ Previous BOM listed Parker 442F42 — WRONG (only rated 114 PSI max)</t>
         </is>
       </c>
       <c r="E11" s="17" t="inlineStr">
         <is>
-          <t>SS316, set pressure adjustable, protects vessel from overpressure</t>
+          <t>316SS, 1/4" tube, rated to 6,000 PSI — matches existing Swagelok fittings
+Set between operating pressure (4,061 PSI) and vessel MAWP (4,999 PSI)
+Recommend set pressure: 4,350 PSI (30 MPa)</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Swagelok authorized distributor</t>
         </is>
       </c>
       <c r="G11" s="17" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="18" t="n">
-        <v>165</v>
+        <v>250</v>
       </c>
       <c r="I11" s="18" t="n">
-        <v>165</v>
+        <v>250</v>
       </c>
       <c r="J11" s="19" t="inlineStr">
         <is>
@@ -1679,7 +1683,7 @@
         </is>
       </c>
       <c r="I23" s="27" t="n">
-        <v>2810</v>
+        <v>2895</v>
       </c>
       <c r="J23" s="26" t="inlineStr"/>
     </row>
@@ -2097,7 +2101,7 @@
         </is>
       </c>
       <c r="I33" s="33" t="n">
-        <v>2810</v>
+        <v>2895</v>
       </c>
       <c r="J33" s="32" t="inlineStr"/>
     </row>

--- a/scCO2_Full_Bill_of_Materials.xlsx
+++ b/scCO2_Full_Bill_of_Materials.xlsx
@@ -632,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1210,46 +1210,50 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>7. Sensors</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>Pressure transducer</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>K4708</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>Ashcroft 0-5000 PSI pressure transducer, 4-20 mA output, SS, IP67</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr">
-        <is>
-          <t>4-20 mA → 1-5 V via 250 ohm shunt resistor into ADS1115 A0</t>
-        </is>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
-        <is>
-          <t>Grainger</t>
-        </is>
-      </c>
-      <c r="G13" s="20" t="n">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>6. Relief Valve</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Vent solenoid valve (automated depressurization)</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>Parker 4-Way or Asco 8290 HP</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>Normally-closed 24VDC solenoid valve, 1/4" tube or NPT, high-pressure rated
+Driven by RPi GPIO 18 (PWM) via relay — opens automatically during DEPRESSURIZE state
+⚠ MUST be rated ≥ 6,000 PSI — standard solenoids (150-300 PSI) will fail catastrophically</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>316SS body, NC (fail-safe closed), 24VDC coil, 1/4" process connection
+Candidates: Parker Series 34 HP, Asco 8290 HP series, or HiP solenoid valve
+⚠ THIS PART IS MISSING FROM ORIGINAL BOM — confirm spec with distributor before ordering</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>Parker / Asco / High Pressure Equipment (HiP)</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="21" t="n">
-        <v>400</v>
-      </c>
-      <c r="I13" s="21" t="n">
-        <v>400</v>
-      </c>
-      <c r="J13" s="22" t="inlineStr">
+      <c r="H13" s="18" t="n">
+        <v>500</v>
+      </c>
+      <c r="I13" s="18" t="n">
+        <v>500</v>
+      </c>
+      <c r="J13" s="19" t="inlineStr">
         <is>
           <t>Search this part</t>
         </is>
@@ -1263,22 +1267,25 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Pressure gauge (mechanical, visual backup)</t>
+          <t>Pressure transducer</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>K4201</t>
+          <t>5DEK9</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Ashcroft 0-5000 PSI analog pressure gauge</t>
+          <t>Ashcroft G2, 0-5000 PSI, 4-20 mA output, nylon housing, 316SS wetted parts, IP67
+Grainger item 5DEK9 — Mfr model G17M0242F25000#
+⚠ Do NOT order K4708 — that is the 1-5V DC output version, incompatible with 4-20mA wiring</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Visual reference gauge, independent of electronics</t>
+          <t>4-20 mA → 1-5 V via 250 ohm shunt resistor into ADS1115 A0
+Nylon housing is fine for lab use; 316SS diaphragm is the CO2-wetted part</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -1290,58 +1297,58 @@
         <v>1</v>
       </c>
       <c r="H14" s="21" t="n">
+        <v>200</v>
+      </c>
+      <c r="I14" s="21" t="n">
+        <v>200</v>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>Search this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>7. Sensors</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>Pressure gauge (mechanical, visual backup)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>K4201</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>Ashcroft 0-5000 PSI analog pressure gauge</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>Visual reference gauge, independent of electronics</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>Grainger</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="21" t="n">
         <v>100</v>
       </c>
-      <c r="I14" s="21" t="n">
+      <c r="I15" s="21" t="n">
         <v>100</v>
       </c>
-      <c r="J14" s="22" t="inlineStr">
-        <is>
-          <t>Search this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>8. Electronics &amp; Control</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>Raspberry Pi 4 (4 GB)</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>RPi4-4GB</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>Single-board computer, runs the 10 Hz control loop in Python 3.11</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>4 GB RAM model recommended</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>Amazon / Adafruit</t>
-        </is>
-      </c>
-      <c r="G15" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="24" t="n">
-        <v>55</v>
-      </c>
-      <c r="I15" s="24" t="n">
-        <v>55</v>
-      </c>
-      <c r="J15" s="25" t="inlineStr">
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>Search this part</t>
         </is>
@@ -1355,37 +1362,37 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>ADS1115 16-bit I2C ADC module</t>
+          <t>Raspberry Pi 4 (4 GB)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>ADS1115</t>
+          <t>RPi4-4GB</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>Reads pressure transducer (A0) and temperature sensor (A1)</t>
+          <t>Single-board computer, runs the 10 Hz control loop in Python 3.11</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
-          <t>16-bit resolution, I2C interface</t>
+          <t>4 GB RAM model recommended</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>Adafruit / Amazon</t>
+          <t>Amazon / Adafruit</t>
         </is>
       </c>
       <c r="G16" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="J16" s="25" t="inlineStr">
         <is>
@@ -1401,37 +1408,37 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>NEMA 17 stepper motor</t>
+          <t>ADS1115 16-bit I2C ADC module</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>NEMA17-200</t>
+          <t>ADS1115</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>Actuates the motorized needle valve via shaft coupler</t>
+          <t>Reads pressure transducer (A0) and temperature sensor (A1)</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
-          <t>200 steps/rev, standard NEMA 17 frame</t>
+          <t>16-bit resolution, I2C interface</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Adafruit / Amazon</t>
         </is>
       </c>
       <c r="G17" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J17" s="25" t="inlineStr">
         <is>
@@ -1447,37 +1454,37 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>A4988 stepper driver</t>
+          <t>NEMA 17 stepper motor</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>A4988</t>
+          <t>NEMA17-200</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>Drives NEMA 17 at 1/16 microstepping; GPIO 17 STEP, 27 DIR, 22 EN</t>
+          <t>Actuates the motorized needle valve via shaft coupler</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>1/16 microstepping driver module</t>
+          <t>200 steps/rev, standard NEMA 17 frame</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>Pololu / Amazon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G18" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J18" s="25" t="inlineStr">
         <is>
@@ -1493,37 +1500,37 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>32 GB microSD card</t>
+          <t>A4988 stepper driver</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>microSD-32GB</t>
+          <t>A4988</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>Boot media for Raspberry Pi 4</t>
+          <t>Drives NEMA 17 at 1/16 microstepping; GPIO 17 STEP, 27 DIR, 22 EN</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
-          <t>Class 10 / A1 rated for reliability</t>
+          <t>1/16 microstepping driver module</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t>Amazon (SanDisk)</t>
+          <t>Pololu / Amazon</t>
         </is>
       </c>
       <c r="G19" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J19" s="25" t="inlineStr">
         <is>
@@ -1539,27 +1546,27 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>Relay module, 24VDC</t>
+          <t>32 GB microSD card</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>Relay-24VDC</t>
+          <t>microSD-32GB</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>Drives vent solenoid from GPIO 18 PWM signal</t>
+          <t>Boot media for Raspberry Pi 4</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>24VDC coil, panel/DIN mountable</t>
+          <t>Class 10 / A1 rated for reliability</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Amazon (SanDisk)</t>
         </is>
       </c>
       <c r="G20" s="23" t="n">
@@ -1585,37 +1592,37 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>DIN rail relay, 24VDC coil</t>
+          <t>Relay module, 24VDC</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>DIN-Relay-24VDC</t>
+          <t>Relay-24VDC</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>DIN-rail mounted relay for panel-style wiring</t>
+          <t>Drives vent solenoid from GPIO 18 PWM signal</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t>24VDC coil</t>
+          <t>24VDC coil, panel/DIN mountable</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G21" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I21" s="24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J21" s="25" t="inlineStr">
         <is>
@@ -1631,22 +1638,22 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>DIN rail power supply, 24VDC 50W</t>
+          <t>DIN rail relay, 24VDC coil</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>33NT20</t>
+          <t>DIN-Relay-24VDC</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>Dayton DIN rail PSU — powers relay, solenoid, and sensor circuits</t>
+          <t>DIN-rail mounted relay for panel-style wiring</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
         <is>
-          <t>24VDC, 50W output</t>
+          <t>24VDC coil</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
@@ -1658,78 +1665,80 @@
         <v>1</v>
       </c>
       <c r="H22" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="I22" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="J22" s="25" t="inlineStr">
+        <is>
+          <t>Search this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>8. Electronics &amp; Control</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>DIN rail power supply, 24VDC 50W</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>33NT20</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>Dayton DIN rail PSU — powers relay, solenoid, and sensor circuits</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>24VDC, 50W output</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>Grainger</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="24" t="n">
         <v>55</v>
       </c>
-      <c r="I22" s="24" t="n">
+      <c r="I23" s="24" t="n">
         <v>55</v>
       </c>
-      <c r="J22" s="25" t="inlineStr">
+      <c r="J23" s="25" t="inlineStr">
         <is>
           <t>Search this part</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="26" t="inlineStr"/>
-      <c r="B23" s="26" t="inlineStr"/>
-      <c r="C23" s="26" t="inlineStr"/>
-      <c r="D23" s="26" t="inlineStr"/>
-      <c r="E23" s="26" t="inlineStr"/>
-      <c r="F23" s="26" t="inlineStr"/>
-      <c r="G23" s="26" t="inlineStr"/>
-      <c r="H23" s="26" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="26" t="inlineStr"/>
+      <c r="B24" s="26" t="inlineStr"/>
+      <c r="C24" s="26" t="inlineStr"/>
+      <c r="D24" s="26" t="inlineStr"/>
+      <c r="E24" s="26" t="inlineStr"/>
+      <c r="F24" s="26" t="inlineStr"/>
+      <c r="G24" s="26" t="inlineStr"/>
+      <c r="H24" s="26" t="inlineStr">
         <is>
           <t>SUBTOTAL (to buy)</t>
         </is>
       </c>
-      <c r="I23" s="27" t="n">
-        <v>2895</v>
-      </c>
-      <c r="J23" s="26" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>9. Already Owned</t>
-        </is>
-      </c>
-      <c r="B24" s="28" t="inlineStr">
-        <is>
-          <t>Pressure vessel</t>
-        </is>
-      </c>
-      <c r="C24" s="28" t="inlineStr">
-        <is>
-          <t>PARR 2302HC</t>
-        </is>
-      </c>
-      <c r="D24" s="28" t="inlineStr">
-        <is>
-          <t>316SS pressure vessel, S/N 4540-1803-78845A, 1 L volume</t>
-        </is>
-      </c>
-      <c r="E24" s="28" t="inlineStr">
-        <is>
-          <t>MAWP 5,000 PSI (34.47 MPa) @ 350°C — no purchase needed</t>
-        </is>
-      </c>
-      <c r="F24" s="28" t="inlineStr">
-        <is>
-          <t>N/A — already owned</t>
-        </is>
-      </c>
-      <c r="G24" s="28" t="inlineStr"/>
-      <c r="H24" s="28" t="inlineStr"/>
-      <c r="I24" s="28" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="J24" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="I24" s="27" t="n">
+        <v>3195</v>
+      </c>
+      <c r="J24" s="26" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="28" t="inlineStr">
@@ -1739,22 +1748,22 @@
       </c>
       <c r="B25" s="28" t="inlineStr">
         <is>
-          <t>Gas booster pump</t>
+          <t>Pressure vessel</t>
         </is>
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>HII 5G-TD-28/150-CO2</t>
+          <t>PARR 2302HC</t>
         </is>
       </c>
       <c r="D25" s="28" t="inlineStr">
         <is>
-          <t>Air-driven, twin-drive CO2 service booster, S/N 1205101</t>
+          <t>316SS pressure vessel, S/N 4540-1803-78845A, 1 L volume</t>
         </is>
       </c>
       <c r="E25" s="28" t="inlineStr">
         <is>
-          <t>Max outlet 25,000 PSIG (172 MPa) — no purchase needed</t>
+          <t>MAWP 5,000 PSI (34.47 MPa) @ 350°C — no purchase needed</t>
         </is>
       </c>
       <c r="F25" s="28" t="inlineStr">
@@ -1783,22 +1792,22 @@
       </c>
       <c r="B26" s="28" t="inlineStr">
         <is>
-          <t>Temperature controller</t>
+          <t>Gas booster pump</t>
         </is>
       </c>
       <c r="C26" s="28" t="inlineStr">
         <is>
-          <t>INKBIRD</t>
+          <t>HII 5G-TD-28/150-CO2</t>
         </is>
       </c>
       <c r="D26" s="28" t="inlineStr">
         <is>
-          <t>60C setpoint temperature controller</t>
+          <t>Air-driven, twin-drive CO2 service booster, S/N 1205101</t>
         </is>
       </c>
       <c r="E26" s="28" t="inlineStr">
         <is>
-          <t>±0.01°C settled stability — no purchase needed</t>
+          <t>Max outlet 25,000 PSIG (172 MPa) — no purchase needed</t>
         </is>
       </c>
       <c r="F26" s="28" t="inlineStr">
@@ -1827,22 +1836,22 @@
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>CO2 gas cylinder</t>
+          <t>Temperature controller</t>
         </is>
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>UN1013 Bone Dry</t>
+          <t>INKBIRD</t>
         </is>
       </c>
       <c r="D27" s="28" t="inlineStr">
         <is>
-          <t>Primary process gas — Metro Welding Supply, Detroit MI</t>
+          <t>60C setpoint temperature controller</t>
         </is>
       </c>
       <c r="E27" s="28" t="inlineStr">
         <is>
-          <t>No purchase needed (existing supply)</t>
+          <t>±0.01°C settled stability — no purchase needed</t>
         </is>
       </c>
       <c r="F27" s="28" t="inlineStr">
@@ -1871,17 +1880,17 @@
       </c>
       <c r="B28" s="28" t="inlineStr">
         <is>
-          <t>N2 gas cylinder</t>
+          <t>CO2 gas cylinder</t>
         </is>
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>UN1066 Ultra High Purity</t>
+          <t>UN1013 Bone Dry</t>
         </is>
       </c>
       <c r="D28" s="28" t="inlineStr">
         <is>
-          <t>Alternate experiment gas — Metro Welding Supply, Detroit MI</t>
+          <t>Primary process gas — Metro Welding Supply, Detroit MI</t>
         </is>
       </c>
       <c r="E28" s="28" t="inlineStr">
@@ -1915,12 +1924,12 @@
       </c>
       <c r="B29" s="28" t="inlineStr">
         <is>
-          <t>Ar gas cylinder</t>
+          <t>N2 gas cylinder</t>
         </is>
       </c>
       <c r="C29" s="28" t="inlineStr">
         <is>
-          <t>UN1006 Prepurified</t>
+          <t>UN1066 Ultra High Purity</t>
         </is>
       </c>
       <c r="D29" s="28" t="inlineStr">
@@ -1959,17 +1968,17 @@
       </c>
       <c r="B30" s="28" t="inlineStr">
         <is>
-          <t>Air gas cylinder (drive air)</t>
+          <t>Ar gas cylinder</t>
         </is>
       </c>
       <c r="C30" s="28" t="inlineStr">
         <is>
-          <t>UN1002 Dry Grade</t>
+          <t>UN1006 Prepurified</t>
         </is>
       </c>
       <c r="D30" s="28" t="inlineStr">
         <is>
-          <t>Drives booster pump only — never enters vessel</t>
+          <t>Alternate experiment gas — Metro Welding Supply, Detroit MI</t>
         </is>
       </c>
       <c r="E30" s="28" t="inlineStr">
@@ -1996,48 +2005,46 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="inlineStr">
-        <is>
-          <t>10. Optional: Windowed Vessel</t>
-        </is>
-      </c>
-      <c r="B31" s="29" t="inlineStr">
-        <is>
-          <t>Windowed pressure vessel (sapphire window)</t>
-        </is>
-      </c>
-      <c r="C31" s="29" t="inlineStr">
-        <is>
-          <t>EZE-Seal series</t>
-        </is>
-      </c>
-      <c r="D31" s="29" t="inlineStr">
-        <is>
-          <t>Autoclave Engineers (Parker) windowed reactor for flow visualization</t>
-        </is>
-      </c>
-      <c r="E31" s="29" t="inlineStr">
-        <is>
-          <t>Sapphire window, up to 60 MPa</t>
-        </is>
-      </c>
-      <c r="F31" s="29" t="inlineStr">
-        <is>
-          <t>Autoclave Engineers (Parker)</t>
-        </is>
-      </c>
-      <c r="G31" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="30" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I31" s="30" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J31" s="31" t="inlineStr">
-        <is>
-          <t>Search this part</t>
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>9. Already Owned</t>
+        </is>
+      </c>
+      <c r="B31" s="28" t="inlineStr">
+        <is>
+          <t>Air gas cylinder (drive air)</t>
+        </is>
+      </c>
+      <c r="C31" s="28" t="inlineStr">
+        <is>
+          <t>UN1002 Dry Grade</t>
+        </is>
+      </c>
+      <c r="D31" s="28" t="inlineStr">
+        <is>
+          <t>Drives booster pump only — never enters vessel</t>
+        </is>
+      </c>
+      <c r="E31" s="28" t="inlineStr">
+        <is>
+          <t>No purchase needed (existing supply)</t>
+        </is>
+      </c>
+      <c r="F31" s="28" t="inlineStr">
+        <is>
+          <t>N/A — already owned</t>
+        </is>
+      </c>
+      <c r="G31" s="28" t="inlineStr"/>
+      <c r="H31" s="28" t="inlineStr"/>
+      <c r="I31" s="28" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="J31" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -2049,61 +2056,107 @@
       </c>
       <c r="B32" s="29" t="inlineStr">
         <is>
-          <t>Windowed pressure vessel (alternate)</t>
+          <t>Windowed pressure vessel (sapphire window)</t>
         </is>
       </c>
       <c r="C32" s="29" t="inlineStr">
         <is>
-          <t>Sitec 100-600 mL</t>
+          <t>EZE-Seal series</t>
         </is>
       </c>
       <c r="D32" s="29" t="inlineStr">
         <is>
-          <t>Sitec Reactor Technology windowed reactor, sapphire/borosilicate</t>
+          <t>Autoclave Engineers (Parker) windowed reactor for flow visualization</t>
         </is>
       </c>
       <c r="E32" s="29" t="inlineStr">
         <is>
-          <t>Up to 100 MPa, 100-600 mL volume</t>
+          <t>Sapphire window, up to 60 MPa</t>
         </is>
       </c>
       <c r="F32" s="29" t="inlineStr">
         <is>
-          <t>Sitec Reactor Technology</t>
+          <t>Autoclave Engineers (Parker)</t>
         </is>
       </c>
       <c r="G32" s="29" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="30" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I32" s="30" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J32" s="31" t="inlineStr">
+        <is>
+          <t>Search this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="inlineStr">
+        <is>
+          <t>10. Optional: Windowed Vessel</t>
+        </is>
+      </c>
+      <c r="B33" s="29" t="inlineStr">
+        <is>
+          <t>Windowed pressure vessel (alternate)</t>
+        </is>
+      </c>
+      <c r="C33" s="29" t="inlineStr">
+        <is>
+          <t>Sitec 100-600 mL</t>
+        </is>
+      </c>
+      <c r="D33" s="29" t="inlineStr">
+        <is>
+          <t>Sitec Reactor Technology windowed reactor, sapphire/borosilicate</t>
+        </is>
+      </c>
+      <c r="E33" s="29" t="inlineStr">
+        <is>
+          <t>Up to 100 MPa, 100-600 mL volume</t>
+        </is>
+      </c>
+      <c r="F33" s="29" t="inlineStr">
+        <is>
+          <t>Sitec Reactor Technology</t>
+        </is>
+      </c>
+      <c r="G33" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="30" t="n">
         <v>4500</v>
       </c>
-      <c r="I32" s="30" t="n">
+      <c r="I33" s="30" t="n">
         <v>4500</v>
       </c>
-      <c r="J32" s="31" t="inlineStr">
+      <c r="J33" s="31" t="inlineStr">
         <is>
           <t>Search this part</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="32" t="inlineStr"/>
-      <c r="B33" s="32" t="inlineStr"/>
-      <c r="C33" s="32" t="inlineStr"/>
-      <c r="D33" s="32" t="inlineStr"/>
-      <c r="E33" s="32" t="inlineStr"/>
-      <c r="F33" s="32" t="inlineStr"/>
-      <c r="G33" s="32" t="inlineStr"/>
-      <c r="H33" s="32" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="32" t="inlineStr"/>
+      <c r="B34" s="32" t="inlineStr"/>
+      <c r="C34" s="32" t="inlineStr"/>
+      <c r="D34" s="32" t="inlineStr"/>
+      <c r="E34" s="32" t="inlineStr"/>
+      <c r="F34" s="32" t="inlineStr"/>
+      <c r="G34" s="32" t="inlineStr"/>
+      <c r="H34" s="32" t="inlineStr">
         <is>
           <t>TOTAL (required, excl. optional window vessel)</t>
         </is>
       </c>
-      <c r="I33" s="33" t="n">
-        <v>2895</v>
-      </c>
-      <c r="J33" s="32" t="inlineStr"/>
+      <c r="I34" s="33" t="n">
+        <v>3195</v>
+      </c>
+      <c r="J34" s="32" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2128,8 +2181,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2141,7 +2195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -2243,64 +2297,109 @@
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>Section 9 (Already Owned) lists existing lab equipment for completeness — no purchase needed.</t>
+          <t>CORRECTIONS vs ORIGINAL BOM:</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>Section 10 (Optional) is a windowed vessel upgrade for visualizing scCO2 flow — not required</t>
+          <t>- Pressure transducer changed from K4708 to 5DEK9 (G17M0242F25000#). K4708 is the 1-5V DC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>for the current closed-vessel system.</t>
+          <t xml:space="preserve">  output variant — incompatible with the 4-20mA → 250Ω shunt wiring already designed.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr"/>
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5DEK9 is the correct 4-20mA version at roughly half the price (~$200 vs ~$400).</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>Recommended buying order:</t>
+          <t>- Vent solenoid valve added (was missing from original BOM). Must be rated ≥6,000 PSI.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>1. Confirm thread/tube size compatibility with the existing PARR vessel fittings before ordering.</t>
+          <t xml:space="preserve">  Standard 150-300 PSI solenoids WILL FAIL at 28 MPa. See Section 6 entry.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="35" t="inlineStr">
-        <is>
-          <t>2. Order Swagelok parts from an authorized distributor when possible (warranty/traceability</t>
-        </is>
-      </c>
+      <c r="A22" s="35" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   matters on a 28 MPa system).</t>
+          <t>Section 9 (Already Owned) lists existing lab equipment for completeness — no purchase needed.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="35" t="inlineStr">
         <is>
-          <t>3. McMaster-Carr ships fastest for tubing; Grainger for relief valve, gauges, and PSU.</t>
+          <t>Section 10 (Optional) is a windowed vessel upgrade for visualizing scCO2 flow — not required</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="35" t="inlineStr">
+        <is>
+          <t>for the current closed-vessel system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="35" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="35" t="inlineStr">
+        <is>
+          <t>Recommended buying order:</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="35" t="inlineStr">
+        <is>
+          <t>1. Confirm thread/tube size compatibility with the existing PARR vessel fittings before ordering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="35" t="inlineStr">
+        <is>
+          <t>2. Order Swagelok parts from an authorized distributor when possible (warranty/traceability</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   matters on a 28 MPa system).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="35" t="inlineStr">
+        <is>
+          <t>3. McMaster-Carr ships fastest for tubing; Grainger for relief valve, gauges, and PSU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="35" t="inlineStr">
         <is>
           <t>4. Electronics (Pi, ADC, stepper driver) are low-risk — any reputable seller is fine.</t>
         </is>

--- a/scCO2_Full_Bill_of_Materials.xlsx
+++ b/scCO2_Full_Bill_of_Materials.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Full BOM" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Notes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Notes &amp; Safety" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -636,15 +636,15 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -695,7 +695,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Buy / Search Link</t>
+          <t>Direct Product Link</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>idealvac.com / Swagelok distributor</t>
+          <t>Swagelok authorized distributor</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>5mm to 1/4" flexible shaft coupler</t>
+          <t>5mm × 1/4" (6.35mm) flexible shaft coupler</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Couples existing NEMA 17 stepper directly to valve stem</t>
+          <t>Couples NEMA 17 stepper motor (5mm shaft) to SS-1RS4 valve stem (1/4")</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Aluminum flexible coupling, 5mm x 1/4"</t>
+          <t>Aluminum flexible coupling, 5mm × 6.35mm (1/4")</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Amazon / Radwell.com</t>
+          <t>Swagelok authorized distributor</t>
         </is>
       </c>
       <c r="G4" s="5" t="n">
@@ -833,7 +833,7 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Radwell.com / eBay (surplus)</t>
+          <t>Swagelok authorized distributor</t>
         </is>
       </c>
       <c r="G5" s="8" t="n">
@@ -879,7 +879,7 @@
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>SS tubing, 1/4" OD x 0.065" wall</t>
+          <t>SS tubing, 1/4" OD × 0.065" wall</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -901,17 +901,19 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Swagelok seamless 316SS tubing, 20 ft minimum order</t>
+          <t>Seamless 316SS tubing, 20 ft coil — ASTM A269
+⚠ Must be 0.065" wall (rated ~7,400 PSI)
+⚠ Amazon B0BB1122VJ (FITOK) is only 0.035" wall (~3,200 PSI) — NOT safe for this system</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>316SS seamless, 1/4" OD x 0.065" wall, 20 ft</t>
+          <t>316SS seamless, 1/4" OD × 0.065" wall, 20 ft</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>mcmaster.com</t>
+          <t>McMaster-Carr</t>
         </is>
       </c>
       <c r="G6" s="11" t="n">
@@ -925,7 +927,7 @@
       </c>
       <c r="J6" s="13" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -957,7 +959,7 @@
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Amazon / Walmart</t>
+          <t>Swagelok authorized distributor</t>
         </is>
       </c>
       <c r="G7" s="14" t="n">
@@ -971,7 +973,7 @@
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1005,7 @@
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Amazon / Walmart</t>
+          <t>Swagelok authorized distributor</t>
         </is>
       </c>
       <c r="G8" s="14" t="n">
@@ -1017,7 +1019,7 @@
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1051,7 @@
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Amazon / Walmart</t>
+          <t>Swagelok authorized distributor</t>
         </is>
       </c>
       <c r="G9" s="14" t="n">
@@ -1063,7 +1065,7 @@
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1097,7 @@
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Swagelok authorized distributor</t>
         </is>
       </c>
       <c r="G10" s="14" t="n">
@@ -1109,7 +1111,7 @@
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -1126,21 +1128,20 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>SS-RL3S4</t>
+          <t>SS-4R3A</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>Swagelok high-pressure relief valve, 1/4" tube compression fitting
-⚠ MUST specify set pressure ~4,350 PSI (30 MPa) when ordering
-⚠ Previous BOM listed Parker 442F42 — WRONG (only rated 114 PSI max)</t>
+          <t>Swagelok HIGH-PRESSURE proportional relief valve, 1/4" tube compression
+⚠ MUST specify set pressure ~4,350 PSI (30 MPa) when ordering from distributor
+⚠ SS-RL3S4 (previously listed) is LOW-PRESSURE only (max 225 PSI) — DANGEROUS for this system</t>
         </is>
       </c>
       <c r="E11" s="17" t="inlineStr">
         <is>
-          <t>316SS, 1/4" tube, rated to 6,000 PSI — matches existing Swagelok fittings
-Set between operating pressure (4,061 PSI) and vessel MAWP (4,999 PSI)
-Recommend set pressure: 4,350 PSI (30 MPa)</t>
+          <t>316SS, 1/4" tube, rated to 6,000 PSI
+Set pressure: 4,350 PSI (30 MPa) — between operating P (4,061 PSI) and MAWP (4,999 PSI)</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
@@ -1159,7 +1160,7 @@
       </c>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -1171,41 +1172,45 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>PTFE thread tape</t>
+          <t>Vent solenoid valve (automated depressurization)</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>34P209</t>
+          <t>Parker Series 34 HP / Asco 8290 HP</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>PTFE sealing tape for NPT thread connections</t>
+          <t>Normally-closed 24VDC solenoid valve, 1/4" tube or NPT, HIGH-pressure rated
+Driven by RPi GPIO 18 via relay — opens automatically during DEPRESSURIZE state
+⚠ MUST be rated ≥ 6,000 PSI — standard solenoids (150-300 PSI) will fail catastrophically
+⚠ This part was MISSING from the original BOM</t>
         </is>
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t>High-pressure / high-temp rated</t>
+          <t>316SS body, NC (fail-safe closed), 24VDC coil, 1/4" process connection
+Candidates: Parker Series 34 HP, Asco 8290 HP, HiP solenoid valve</t>
         </is>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Parker / Asco / High Pressure Equipment</t>
         </is>
       </c>
       <c r="G12" s="17" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="J12" s="19" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -1217,45 +1222,41 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>Vent solenoid valve (automated depressurization)</t>
+          <t>PTFE thread tape</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>Parker 4-Way or Asco 8290 HP</t>
+          <t>34P209</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>Normally-closed 24VDC solenoid valve, 1/4" tube or NPT, high-pressure rated
-Driven by RPi GPIO 18 (PWM) via relay — opens automatically during DEPRESSURIZE state
-⚠ MUST be rated ≥ 6,000 PSI — standard solenoids (150-300 PSI) will fail catastrophically</t>
+          <t>PTFE sealing tape for NPT thread connections</t>
         </is>
       </c>
       <c r="E13" s="17" t="inlineStr">
         <is>
-          <t>316SS body, NC (fail-safe closed), 24VDC coil, 1/4" process connection
-Candidates: Parker Series 34 HP, Asco 8290 HP series, or HiP solenoid valve
-⚠ THIS PART IS MISSING FROM ORIGINAL BOM — confirm spec with distributor before ordering</t>
+          <t>High-pressure / high-temp rated</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>Parker / Asco / High Pressure Equipment (HiP)</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="G13" s="17" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>500</v>
+        <v>5</v>
       </c>
       <c r="I13" s="18" t="n">
-        <v>500</v>
+        <v>5</v>
       </c>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1305,7 @@
       </c>
       <c r="J14" s="22" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1351,7 @@
       </c>
       <c r="J15" s="22" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1363,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Raspberry Pi 4 (4 GB)</t>
+          <t>Raspberry Pi 4 — CanaKit Starter Pro Kit (4 GB)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -1372,31 +1373,32 @@
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>Single-board computer, runs the 10 Hz control loop in Python 3.11</t>
+          <t>CanaKit Starter Pro Kit: RPi4 4GB + case + 3.5A power supply + 32GB SD card + heatsinks
+SD card is INCLUDED in this kit — do NOT buy the separate microSD card listed below</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
-          <t>4 GB RAM model recommended</t>
+          <t>4 GB RAM, includes 32GB pre-loaded SD card, case, power supply</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>Amazon / Adafruit</t>
+          <t>Amazon — CanaKit</t>
         </is>
       </c>
       <c r="G16" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="J16" s="25" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1425,12 @@
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
-          <t>16-bit resolution, I2C interface</t>
+          <t>16-bit resolution, I2C interface, Raspberry Pi compatible</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t>Adafruit / Amazon</t>
+          <t>Amazon — Qoroos (3-pack)</t>
         </is>
       </c>
       <c r="G17" s="23" t="n">
@@ -1442,7 +1444,7 @@
       </c>
       <c r="J17" s="25" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1471,12 @@
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>200 steps/rev, standard NEMA 17 frame</t>
+          <t>200 steps/rev, bipolar, NEMA 17 frame</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Amazon — STEPPERONLINE</t>
         </is>
       </c>
       <c r="G18" s="23" t="n">
@@ -1488,7 +1490,7 @@
       </c>
       <c r="J18" s="25" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1522,7 @@
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t>Pololu / Amazon</t>
+          <t>Amazon — HiLetgo</t>
         </is>
       </c>
       <c r="G19" s="23" t="n">
@@ -1534,7 +1536,7 @@
       </c>
       <c r="J19" s="25" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1548,7 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>32 GB microSD card</t>
+          <t>32 GB microSD card (optional — included in CanaKit)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -1556,7 +1558,7 @@
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>Boot media for Raspberry Pi 4</t>
+          <t>Boot media for Raspberry Pi 4 — SKIP if using CanaKit B07V5JTMV9 (already included)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -1580,7 +1582,7 @@
       </c>
       <c r="J20" s="25" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -1592,27 +1594,29 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>Relay module, 24VDC</t>
+          <t>Relay module — RPi-compatible (3.3V trigger)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>Relay-24VDC</t>
+          <t>Relay-5V-Optocoupler</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>Drives vent solenoid from GPIO 18 PWM signal</t>
+          <t>Optocoupler-isolated relay module. RPi GPIO 18 (3.3V) → relay IN → switches 24VDC to solenoid
+⚠ GAEYAELE B07DYLKH74 (prev BOM) requires 24VDC trigger — NOT compatible with RPi 3.3V GPIO
+Must be optocoupler-isolated relay accepting 3.3V–5V logic trigger signal</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t>24VDC coil, panel/DIN mountable</t>
+          <t>5V coil, optocoupler isolated, accepts 3.3V RPi GPIO trigger, 1-channel minimum</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Amazon — search: relay module 5V optocoupler raspberry pi</t>
         </is>
       </c>
       <c r="G21" s="23" t="n">
@@ -1626,7 +1630,7 @@
       </c>
       <c r="J21" s="25" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1652,7 @@
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>DIN-rail mounted relay for panel-style wiring</t>
+          <t>DIN-rail mounted relay for panel-style wiring of solenoid circuit</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -1672,7 +1676,7 @@
       </c>
       <c r="J22" s="25" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1722,7 @@
       </c>
       <c r="J23" s="25" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1740,7 @@
         </is>
       </c>
       <c r="I24" s="27" t="n">
-        <v>3195</v>
+        <v>3240</v>
       </c>
       <c r="J24" s="26" t="inlineStr"/>
     </row>
@@ -2090,7 +2094,7 @@
       </c>
       <c r="J32" s="31" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2140,7 @@
       </c>
       <c r="J33" s="31" t="inlineStr">
         <is>
-          <t>Search this part</t>
+          <t>Open product page</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2158,7 @@
         </is>
       </c>
       <c r="I34" s="33" t="n">
-        <v>3195</v>
+        <v>3240</v>
       </c>
       <c r="J34" s="32" t="inlineStr"/>
     </row>
@@ -2195,16 +2199,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="115" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="34" t="inlineStr">
         <is>
-          <t>scCO2 System — Complete BOM Notes</t>
+          <t>scCO2 System — Complete BOM Notes &amp; Safety Corrections</t>
         </is>
       </c>
     </row>
@@ -2214,149 +2218,141 @@
     <row r="3">
       <c r="A3" s="35" t="inlineStr">
         <is>
-          <t>LINK VERIFICATION DISCLAIMER:</t>
+          <t>LINKS: All links in this BOM are direct product page URLs (not search pages).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="35" t="inlineStr">
         <is>
-          <t>Automated link-checking was not possible in the environment this file was generated in</t>
+          <t>A few items use search URLs where no single confirmed direct product page exists.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
-        <is>
-          <t>(all outbound web requests returned 403, including to sites like Wikipedia — a sandbox</t>
-        </is>
-      </c>
+      <c r="A5" s="35" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>network restriction, not a sign the URLs are wrong). Each link uses the vendor's standard,</t>
+          <t>CRITICAL SAFETY CORRECTIONS (July 2026 audit):</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr">
-        <is>
-          <t>publicly documented search-page URL format with the part number/description as the query</t>
-        </is>
-      </c>
+      <c r="A7" s="35" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>string — not a guessed deep product page. Please click a few to confirm before bulk-ordering.</t>
+          <t>1. RELIEF VALVE — Part changed from SS-RL3S4 to SS-4R3A</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="inlineStr"/>
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   SS-RL3S4 is Swagelok's LOW-PRESSURE series — maximum set pressure 225 PSI.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>Why these exact part numbers matter:</t>
+          <t xml:space="preserve">   Your system operates at 4,061 PSI (28 MPa). SS-RL3S4 would blow open at 225 PSI</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>- SS-CHS4-5 (check valve) is rated 6,000 PSI. SS-4C looks similar but is only 3,000 PSI.</t>
+          <t xml:space="preserve">   and never hold pressure. The correct part is SS-4R3A (HIGH-pressure, up to 6,000 PSI).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>- SS-83KS4 (ball valve) is rated 6,000 PSI. SS-43GS4 looks similar but is only 3,000 PSI.</t>
+          <t xml:space="preserve">   Set pressure must be specified at ordering: recommend 4,350 PSI (30 MPa).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
-        <is>
-          <t>- All fittings are Swagelok SS-400 series, rated 5,100 PSI, matched to 1/4" tube OD.</t>
-        </is>
-      </c>
+      <c r="A13" s="35" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>- SS-1RS4 needle valve (5,000 PSI) gives ~23% margin above 4,061 PSI (28 MPa) operating pressure.</t>
+          <t>2. STAINLESS TUBING — Must be 0.065" wall, NOT 0.035" wall</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr"/>
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Amazon FITOK B0BB1122VJ (1/4" OD x 0.035" wall) is rated ~3,200 PSI — insufficient</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>CORRECTIONS vs ORIGINAL BOM:</t>
+          <t xml:space="preserve">   for 4,061 PSI operation with adequate safety margin. The 0.065" wall version</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>- Pressure transducer changed from K4708 to 5DEK9 (G17M0242F25000#). K4708 is the 1-5V DC</t>
+          <t xml:space="preserve">   (SS-T4-S-065-20) is rated ~7,400 PSI and is the correct choice. Order from McMaster-Carr.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  output variant — incompatible with the 4-20mA → 250Ω shunt wiring already designed.</t>
-        </is>
-      </c>
+      <c r="A18" s="35" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5DEK9 is the correct 4-20mA version at roughly half the price (~$200 vs ~$400).</t>
+          <t>3. RELAY MODULE — Must accept 3.3V RPi GPIO trigger</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>- Vent solenoid valve added (was missing from original BOM). Must be rated ≥6,000 PSI.</t>
+          <t xml:space="preserve">   GAEYAELE B07DYLKH74 requires 24VDC trigger (PLC-grade). Raspberry Pi GPIO 18</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Standard 150-300 PSI solenoids WILL FAIL at 28 MPa. See Section 6 entry.</t>
+          <t xml:space="preserve">   outputs 3.3V — this relay will not fire. Use an optocoupler-isolated relay module</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="35" t="inlineStr"/>
+      <c r="A22" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   with 5V coil that accepts 3.3V logic trigger (common Arduino/RPi relay boards).</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="35" t="inlineStr">
-        <is>
-          <t>Section 9 (Already Owned) lists existing lab equipment for completeness — no purchase needed.</t>
-        </is>
-      </c>
+      <c r="A23" s="35" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="35" t="inlineStr">
         <is>
-          <t>Section 10 (Optional) is a windowed vessel upgrade for visualizing scCO2 flow — not required</t>
+          <t>4. PRESSURE TRANSDUCER — Order item 5DEK9 (4-20 mA), NOT K4708 (1-5V DC)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="35" t="inlineStr">
         <is>
-          <t>for the current closed-vessel system.</t>
+          <t xml:space="preserve">   K4708 has the wrong output type for the 250-ohm shunt wiring designed into the system.</t>
         </is>
       </c>
     </row>
@@ -2366,42 +2362,114 @@
     <row r="27">
       <c r="A27" s="35" t="inlineStr">
         <is>
-          <t>Recommended buying order:</t>
+          <t>5. VENT SOLENOID VALVE — Was missing from original BOM, now added</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="35" t="inlineStr">
         <is>
-          <t>1. Confirm thread/tube size compatibility with the existing PARR vessel fittings before ordering.</t>
+          <t xml:space="preserve">   Must be rated &gt;= 6,000 PSI. Standard solenoids (150-300 PSI) will rupture at 28 MPa.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="35" t="inlineStr">
-        <is>
-          <t>2. Order Swagelok parts from an authorized distributor when possible (warranty/traceability</t>
-        </is>
-      </c>
+      <c r="A29" s="35" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   matters on a 28 MPa system).</t>
+          <t>Why exact Swagelok part numbers matter:</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="35" t="inlineStr">
         <is>
-          <t>3. McMaster-Carr ships fastest for tubing; Grainger for relief valve, gauges, and PSU.</t>
+          <t>- SS-CHS4-5 (check valve): 6,000 PSI. SS-4C looks similar but is only 3,000 PSI.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="35" t="inlineStr">
         <is>
-          <t>4. Electronics (Pi, ADC, stepper driver) are low-risk — any reputable seller is fine.</t>
+          <t>- SS-83KS4 (ball valve): 6,000 PSI. SS-43GS4 looks similar but is only 3,000 PSI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="35" t="inlineStr">
+        <is>
+          <t>- All SS-400 fittings: 5,100 PSI rated, matched to 1/4" tube OD throughout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="35" t="inlineStr">
+        <is>
+          <t>- SS-1RS4 needle valve: 5,000 PSI gives ~23% margin above 4,061 PSI operating pressure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="35" t="inlineStr">
+        <is>
+          <t>CanaKit note: B07V5JTMV9 starter kit includes a 32GB SD card. Do not also buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="35" t="inlineStr">
+        <is>
+          <t>the separate microSD card listed in section 8 — it would be a duplicate purchase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="35" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>Recommended buying order:</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>1. Confirm tube/thread size compatibility with your PARR vessel fittings first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>2. Order Swagelok parts from an authorized distributor (warranty/traceability on 28 MPa system).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>3. Specify set pressure 4,350 PSI when ordering the SS-4R3A relief valve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="35" t="inlineStr">
+        <is>
+          <t>4. McMaster-Carr ships fastest for tubing; Grainger for PSU, gauge, and PTFE tape.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="35" t="inlineStr">
+        <is>
+          <t>5. Electronics (RPi, ADC, stepper driver) — any reputable Amazon seller is fine.</t>
         </is>
       </c>
     </row>

--- a/scCO2_Full_Bill_of_Materials.xlsx
+++ b/scCO2_Full_Bill_of_Materials.xlsx
@@ -903,7 +903,8 @@
         <is>
           <t>Seamless 316SS tubing, 20 ft coil — ASTM A269
 ⚠ Must be 0.065" wall (rated ~7,400 PSI)
-⚠ Amazon B0BB1122VJ (FITOK) is only 0.035" wall (~3,200 PSI) — NOT safe for this system</t>
+⚠ Amazon B0BB1122VJ (FITOK) is only 0.035" wall (~3,200 PSI) — NOT safe for this system
+✓ Amazon B0B9ZV93WP (FITOK Group A) is 0.065" wall — verify spec on product page before ordering</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -913,7 +914,7 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>McMaster-Carr</t>
+          <t>Amazon — FITOK</t>
         </is>
       </c>
       <c r="G6" s="11" t="n">

--- a/scCO2_Full_Bill_of_Materials.xlsx
+++ b/scCO2_Full_Bill_of_Materials.xlsx
@@ -632,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -644,7 +644,7 @@
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -722,7 +722,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>316SS, 5,000 PSI, Cv = 0.37</t>
+          <t>316SS, 5,000 PSI @ 100°F, Cv = 0.37</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>Open product page</t>
+          <t>SS-1RS4</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>5mm × 1/4" (6.35mm) flexible shaft coupler</t>
+          <t>5mm × 6.35mm flexible shaft coupler</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Couples NEMA 17 stepper motor (5mm shaft) to SS-1RS4 valve stem (1/4")</t>
+          <t>Couples NEMA 17 stepper motor (5mm shaft) to SS-1RS4 valve stem (1/4" = 6.35mm)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Aluminum flexible coupling, 5mm × 6.35mm (1/4")</t>
+          <t>Aluminum flexible coupling, 5mm × 6.35mm bores</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Open product page</t>
+          <t>Flexible Shaft Coupler</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>Open product page</t>
+          <t>SS-CHS4-5</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Ball valve</t>
+          <t>Ball valve — vessel inlet isolation</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -855,7 +855,9 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Swagelok 83 series ball valve, 1/4" tube fitting, PCTFE seats, CO2 compatible</t>
+          <t>Swagelok 83 series ball valve, 1/4" tube fitting, PCTFE seats, CO2 compatible
+Only 1 needed — HiP valve on booster outlet covers supply shutoff position;
+SS-3NRM4 already on vessel outlet covers vent isolation position</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -869,17 +871,17 @@
         </is>
       </c>
       <c r="G5" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5" s="9" t="n">
         <v>407</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>1221</v>
+        <v>407</v>
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>Open product page</t>
+          <t>SS-83KS4</t>
         </is>
       </c>
     </row>
@@ -896,39 +898,40 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>SS-T4-S-065-20</t>
+          <t>5LVR1</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Seamless 316SS tubing, 20 ft coil — ASTM A269
-⚠ Must be 0.065" wall (rated ~7,400 PSI)
-⚠ Amazon B0BB1122VJ (FITOK) is only 0.035" wall (~3,200 PSI) — NOT safe for this system
-✓ Amazon B0B9ZV93WP (FITOK Group A) is 0.065" wall — verify spec on product page before ordering</t>
+          <t>Seamless 316SS tubing, 6 ft length — ASTM A213 + A269, annealed
+Buy 3 pieces (18 ft total) for adequate spare — system needs ~10 ft
+⚠ Must be seamless annealed (NOT welded) for Swagelok compression fittings
+⚠ Amazon FITOK B0BB1122VJ is only 0.035" wall (~3,200 PSI) — NOT safe</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>316SS seamless, 1/4" OD × 0.065" wall, 20 ft</t>
+          <t>316SS seamless annealed, 1/4" OD × 0.065" wall, 6 ft per piece
+Rated 8,125 PSI @ 72°F — 2× safety margin over 4,061 PSI operating pressure</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Amazon — FITOK</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="G6" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>120</v>
+        <v>36.43</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>120</v>
+        <v>109.29</v>
       </c>
       <c r="J6" s="13" t="inlineStr">
         <is>
-          <t>Open product page</t>
+          <t>5LVR1 Seamless SS Tubing</t>
         </is>
       </c>
     </row>
@@ -974,7 +977,7 @@
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>Open product page</t>
+          <t>SS-400-6</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1023,7 @@
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>Open product page</t>
+          <t>SS-400-9</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1069,7 @@
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>Open product page</t>
+          <t>SS-400-3</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1115,7 @@
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>Open product page</t>
+          <t>SS-400-C</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1164,7 @@
       </c>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t>Open product page</t>
+          <t>SS-4R3A</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1214,7 @@
       </c>
       <c r="J12" s="19" t="inlineStr">
         <is>
-          <t>Open product page</t>
+          <t>HP Solenoid Valve</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1260,7 @@
       </c>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Open product page</t>
+          <t>34P209 PTFE Tape</t>
         </is>
       </c>
     </row>
@@ -1306,53 +1309,54 @@
       </c>
       <c r="J14" s="22" t="inlineStr">
         <is>
-          <t>Open product page</t>
+          <t>5DEK9 Pressure Transducer</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>7. Sensors</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>Pressure gauge (mechanical, visual backup)</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>K4201</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="inlineStr">
-        <is>
-          <t>Ashcroft 0-5000 PSI analog pressure gauge</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="inlineStr">
-        <is>
-          <t>Visual reference gauge, independent of electronics</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>Grainger</t>
-        </is>
-      </c>
-      <c r="G15" s="20" t="n">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>8. Electronics &amp; Control</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>Raspberry Pi 4 — CanaKit Starter Pro Kit (4 GB)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B07V5JTMV9</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>CanaKit Starter Pro Kit: RPi4 4GB + case + 3.5A power supply + 32GB SD card + heatsinks
+SD card is INCLUDED in this kit — do NOT buy the separate microSD card</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>4 GB RAM, includes 32GB pre-loaded SD card, case, power supply</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>Amazon — CanaKit</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="21" t="n">
+      <c r="H15" s="24" t="n">
         <v>100</v>
       </c>
-      <c r="I15" s="21" t="n">
+      <c r="I15" s="24" t="n">
         <v>100</v>
       </c>
-      <c r="J15" s="22" t="inlineStr">
-        <is>
-          <t>Open product page</t>
+      <c r="J15" s="25" t="inlineStr">
+        <is>
+          <t>CanaKit RPi 4 Starter Kit</t>
         </is>
       </c>
     </row>
@@ -1364,42 +1368,41 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Raspberry Pi 4 — CanaKit Starter Pro Kit (4 GB)</t>
+          <t>ADS1115 16-bit I2C ADC module</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>RPi4-4GB</t>
+          <t>B0DP43DDZG</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>CanaKit Starter Pro Kit: RPi4 4GB + case + 3.5A power supply + 32GB SD card + heatsinks
-SD card is INCLUDED in this kit — do NOT buy the separate microSD card listed below</t>
+          <t>Reads pressure transducer (A0) and temperature sensor (A1)</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
-          <t>4 GB RAM, includes 32GB pre-loaded SD card, case, power supply</t>
+          <t>16-bit resolution, I2C interface, Raspberry Pi compatible</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>Amazon — CanaKit</t>
+          <t>Amazon — Qoroos (3-pack)</t>
         </is>
       </c>
       <c r="G16" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="J16" s="25" t="inlineStr">
         <is>
-          <t>Open product page</t>
+          <t>ADS1115 ADC Module</t>
         </is>
       </c>
     </row>
@@ -1411,41 +1414,41 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>ADS1115 16-bit I2C ADC module</t>
+          <t>NEMA 17 stepper motor</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>ADS1115</t>
+          <t>B00PNEQKC0</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>Reads pressure transducer (A0) and temperature sensor (A1)</t>
+          <t>Actuates the motorized needle valve via shaft coupler</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
-          <t>16-bit resolution, I2C interface, Raspberry Pi compatible</t>
+          <t>200 steps/rev, bipolar, NEMA 17 frame</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t>Amazon — Qoroos (3-pack)</t>
+          <t>Amazon — STEPPERONLINE</t>
         </is>
       </c>
       <c r="G17" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J17" s="25" t="inlineStr">
         <is>
-          <t>Open product page</t>
+          <t>NEMA 17 Stepper Motor</t>
         </is>
       </c>
     </row>
@@ -1457,41 +1460,41 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>NEMA 17 stepper motor</t>
+          <t>A4988 stepper driver</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>NEMA17-200</t>
+          <t>B07BND65C8</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>Actuates the motorized needle valve via shaft coupler</t>
+          <t>Drives NEMA 17 at 1/16 microstepping; GPIO 17 STEP, 27 DIR, 22 EN</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>200 steps/rev, bipolar, NEMA 17 frame</t>
+          <t>1/16 microstepping driver module</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>Amazon — STEPPERONLINE</t>
+          <t>Amazon — HiLetgo</t>
         </is>
       </c>
       <c r="G18" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J18" s="25" t="inlineStr">
         <is>
-          <t>Open product page</t>
+          <t>A4988 Stepper Driver</t>
         </is>
       </c>
     </row>
@@ -1503,41 +1506,43 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>A4988 stepper driver</t>
+          <t>Relay module — RPi-compatible (3.3V trigger)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>A4988</t>
+          <t>B095YD3732</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>Drives NEMA 17 at 1/16 microstepping; GPIO 17 STEP, 27 DIR, 22 EN</t>
+          <t>AEDIKO 1-channel optocoupler-isolated relay module
+RPi GPIO 18 (3.3V) → relay IN → switches 24VDC to solenoid
+⚠ GAEYAELE B07DYLKH74 (prev BOM) requires 24VDC trigger — NOT compatible with RPi 3.3V GPIO</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
-          <t>1/16 microstepping driver module</t>
+          <t>5V coil, optocoupler isolated, accepts 3.3V RPi GPIO trigger, 1-channel</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t>Amazon — HiLetgo</t>
+          <t>Amazon — AEDIKO</t>
         </is>
       </c>
       <c r="G19" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J19" s="25" t="inlineStr">
         <is>
-          <t>Open product page</t>
+          <t>AEDIKO Relay Module</t>
         </is>
       </c>
     </row>
@@ -1549,41 +1554,42 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>32 GB microSD card (optional — included in CanaKit)</t>
+          <t>Jumper wires assorted kit</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>microSD-32GB</t>
+          <t>Dupont Jumper Wires</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>Boot media for Raspberry Pi 4 — SKIP if using CanaKit B07V5JTMV9 (already included)</t>
+          <t>Male-to-female and male-to-male jumper wires for GPIO connections
+RPi GPIO → ADS1115 (4 wires), A4988 (3 wires), relay module (3 wires)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>Class 10 / A1 rated for reliability</t>
+          <t>120-piece assorted kit: male-to-male + male-to-female</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>Amazon (SanDisk)</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G20" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I20" s="24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J20" s="25" t="inlineStr">
         <is>
-          <t>Open product page</t>
+          <t>Jumper Wires Kit</t>
         </is>
       </c>
     </row>
@@ -1595,43 +1601,41 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>Relay module — RPi-compatible (3.3V trigger)</t>
+          <t>DIN rail relay, 24VDC coil</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>Relay-5V-Optocoupler</t>
+          <t>4WAU2</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>Optocoupler-isolated relay module. RPi GPIO 18 (3.3V) → relay IN → switches 24VDC to solenoid
-⚠ GAEYAELE B07DYLKH74 (prev BOM) requires 24VDC trigger — NOT compatible with RPi 3.3V GPIO
-Must be optocoupler-isolated relay accepting 3.3V–5V logic trigger signal</t>
+          <t>DIN-rail mounted relay for panel-style wiring of solenoid circuit (optional for bench setup)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t>5V coil, optocoupler isolated, accepts 3.3V RPi GPIO trigger, 1-channel minimum</t>
+          <t>24VDC coil</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t>Amazon — search: relay module 5V optocoupler raspberry pi</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="G21" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I21" s="24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J21" s="25" t="inlineStr">
         <is>
-          <t>Open product page</t>
+          <t>4WAU2 DIN Rail Relay</t>
         </is>
       </c>
     </row>
@@ -1643,22 +1647,22 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>DIN rail relay, 24VDC coil</t>
+          <t>DIN rail power supply, 24VDC 50W</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>DIN-Relay-24VDC</t>
+          <t>33NT20</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>DIN-rail mounted relay for panel-style wiring of solenoid circuit</t>
+          <t>Dayton DIN rail PSU — powers relay, solenoid, and sensor circuits</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
         <is>
-          <t>24VDC coil</t>
+          <t>24VDC, 50W output</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
@@ -1670,80 +1674,78 @@
         <v>1</v>
       </c>
       <c r="H22" s="24" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="I22" s="24" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="J22" s="25" t="inlineStr">
         <is>
-          <t>Open product page</t>
+          <t>33NT20 DIN Rail PSU</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="23" t="inlineStr">
-        <is>
-          <t>8. Electronics &amp; Control</t>
-        </is>
-      </c>
-      <c r="B23" s="23" t="inlineStr">
-        <is>
-          <t>DIN rail power supply, 24VDC 50W</t>
-        </is>
-      </c>
-      <c r="C23" s="23" t="inlineStr">
-        <is>
-          <t>33NT20</t>
-        </is>
-      </c>
-      <c r="D23" s="23" t="inlineStr">
-        <is>
-          <t>Dayton DIN rail PSU — powers relay, solenoid, and sensor circuits</t>
-        </is>
-      </c>
-      <c r="E23" s="23" t="inlineStr">
-        <is>
-          <t>24VDC, 50W output</t>
-        </is>
-      </c>
-      <c r="F23" s="23" t="inlineStr">
-        <is>
-          <t>Grainger</t>
-        </is>
-      </c>
-      <c r="G23" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="24" t="n">
-        <v>55</v>
-      </c>
-      <c r="I23" s="24" t="n">
-        <v>55</v>
-      </c>
-      <c r="J23" s="25" t="inlineStr">
-        <is>
-          <t>Open product page</t>
-        </is>
-      </c>
+      <c r="A23" s="26" t="inlineStr"/>
+      <c r="B23" s="26" t="inlineStr"/>
+      <c r="C23" s="26" t="inlineStr"/>
+      <c r="D23" s="26" t="inlineStr"/>
+      <c r="E23" s="26" t="inlineStr"/>
+      <c r="F23" s="26" t="inlineStr"/>
+      <c r="G23" s="26" t="inlineStr"/>
+      <c r="H23" s="26" t="inlineStr">
+        <is>
+          <t>SUBTOTAL (to buy)</t>
+        </is>
+      </c>
+      <c r="I23" s="27" t="n">
+        <v>2312.29</v>
+      </c>
+      <c r="J23" s="26" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="inlineStr"/>
-      <c r="B24" s="26" t="inlineStr"/>
-      <c r="C24" s="26" t="inlineStr"/>
-      <c r="D24" s="26" t="inlineStr"/>
-      <c r="E24" s="26" t="inlineStr"/>
-      <c r="F24" s="26" t="inlineStr"/>
-      <c r="G24" s="26" t="inlineStr"/>
-      <c r="H24" s="26" t="inlineStr">
-        <is>
-          <t>SUBTOTAL (to buy)</t>
-        </is>
-      </c>
-      <c r="I24" s="27" t="n">
-        <v>3240</v>
-      </c>
-      <c r="J24" s="26" t="inlineStr"/>
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>9. Already Owned</t>
+        </is>
+      </c>
+      <c r="B24" s="28" t="inlineStr">
+        <is>
+          <t>Pressure vessel</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="inlineStr">
+        <is>
+          <t>PARR 2302HC</t>
+        </is>
+      </c>
+      <c r="D24" s="28" t="inlineStr">
+        <is>
+          <t>316SS pressure vessel, S/N 4540-1803-78845A, 1 L volume</t>
+        </is>
+      </c>
+      <c r="E24" s="28" t="inlineStr">
+        <is>
+          <t>MAWP 5,000 PSI (34.47 MPa) @ 350°C — no purchase needed</t>
+        </is>
+      </c>
+      <c r="F24" s="28" t="inlineStr">
+        <is>
+          <t>N/A — already owned</t>
+        </is>
+      </c>
+      <c r="G24" s="28" t="inlineStr"/>
+      <c r="H24" s="28" t="inlineStr"/>
+      <c r="I24" s="28" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="J24" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="28" t="inlineStr">
@@ -1753,22 +1755,22 @@
       </c>
       <c r="B25" s="28" t="inlineStr">
         <is>
-          <t>Pressure vessel</t>
+          <t>Gas booster pump</t>
         </is>
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>PARR 2302HC</t>
+          <t>HII 5G-TD-28/150-CO2</t>
         </is>
       </c>
       <c r="D25" s="28" t="inlineStr">
         <is>
-          <t>316SS pressure vessel, S/N 4540-1803-78845A, 1 L volume</t>
+          <t>Air-driven, twin-drive CO2 service booster, S/N 1205101</t>
         </is>
       </c>
       <c r="E25" s="28" t="inlineStr">
         <is>
-          <t>MAWP 5,000 PSI (34.47 MPa) @ 350°C — no purchase needed</t>
+          <t>Max outlet 25,000 PSIG (172 MPa) — no purchase needed</t>
         </is>
       </c>
       <c r="F25" s="28" t="inlineStr">
@@ -1797,22 +1799,22 @@
       </c>
       <c r="B26" s="28" t="inlineStr">
         <is>
-          <t>Gas booster pump</t>
+          <t>HiP valve on booster outlet</t>
         </is>
       </c>
       <c r="C26" s="28" t="inlineStr">
         <is>
-          <t>HII 5G-TD-28/150-CO2</t>
+          <t>High Pressure Equipment valve</t>
         </is>
       </c>
       <c r="D26" s="28" t="inlineStr">
         <is>
-          <t>Air-driven, twin-drive CO2 service booster, S/N 1205101</t>
+          <t>Manual shutoff valve already installed on booster HP outlet — covers BV-1 position</t>
         </is>
       </c>
       <c r="E26" s="28" t="inlineStr">
         <is>
-          <t>Max outlet 25,000 PSIG (172 MPa) — no purchase needed</t>
+          <t>No purchase needed — saves ~$407 vs buying SS-83KS4 here</t>
         </is>
       </c>
       <c r="F26" s="28" t="inlineStr">
@@ -1841,22 +1843,23 @@
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>Temperature controller</t>
+          <t>SS-3NRM4 needle valve on vessel outlet</t>
         </is>
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>INKBIRD</t>
+          <t>Swagelok SS-3NRM4</t>
         </is>
       </c>
       <c r="D27" s="28" t="inlineStr">
         <is>
-          <t>60C setpoint temperature controller</t>
+          <t>Manual needle valve already installed on vessel outlet — covers vent isolation position
+⚠ Must remain OPEN during automated operation — solenoid SV-1 controls automated venting</t>
         </is>
       </c>
       <c r="E27" s="28" t="inlineStr">
         <is>
-          <t>±0.01°C settled stability — no purchase needed</t>
+          <t>8,000 PSI rated — no purchase needed — saves ~$407 vs buying SS-83KS4 here</t>
         </is>
       </c>
       <c r="F27" s="28" t="inlineStr">
@@ -1885,22 +1888,22 @@
       </c>
       <c r="B28" s="28" t="inlineStr">
         <is>
-          <t>CO2 gas cylinder</t>
+          <t>Pressure gauge on vessel</t>
         </is>
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>UN1013 Bone Dry</t>
+          <t>Duro United 0-5000 PSI</t>
         </is>
       </c>
       <c r="D28" s="28" t="inlineStr">
         <is>
-          <t>Primary process gas — Metro Welding Supply, Detroit MI</t>
+          <t>Mechanical pressure gauge already installed on PARR vessel port</t>
         </is>
       </c>
       <c r="E28" s="28" t="inlineStr">
         <is>
-          <t>No purchase needed (existing supply)</t>
+          <t>No purchase needed — saves ~$100 vs K4201</t>
         </is>
       </c>
       <c r="F28" s="28" t="inlineStr">
@@ -1929,22 +1932,22 @@
       </c>
       <c r="B29" s="28" t="inlineStr">
         <is>
-          <t>N2 gas cylinder</t>
+          <t>Temperature controller</t>
         </is>
       </c>
       <c r="C29" s="28" t="inlineStr">
         <is>
-          <t>UN1066 Ultra High Purity</t>
+          <t>INKBIRD</t>
         </is>
       </c>
       <c r="D29" s="28" t="inlineStr">
         <is>
-          <t>Alternate experiment gas — Metro Welding Supply, Detroit MI</t>
+          <t>60C setpoint temperature controller</t>
         </is>
       </c>
       <c r="E29" s="28" t="inlineStr">
         <is>
-          <t>No purchase needed (existing supply)</t>
+          <t>±0.01°C settled stability — no purchase needed</t>
         </is>
       </c>
       <c r="F29" s="28" t="inlineStr">
@@ -1973,17 +1976,17 @@
       </c>
       <c r="B30" s="28" t="inlineStr">
         <is>
-          <t>Ar gas cylinder</t>
+          <t>CO2 gas cylinder</t>
         </is>
       </c>
       <c r="C30" s="28" t="inlineStr">
         <is>
-          <t>UN1006 Prepurified</t>
+          <t>UN1013 Bone Dry</t>
         </is>
       </c>
       <c r="D30" s="28" t="inlineStr">
         <is>
-          <t>Alternate experiment gas — Metro Welding Supply, Detroit MI</t>
+          <t>Primary process gas — Metro Welding Supply, Detroit MI</t>
         </is>
       </c>
       <c r="E30" s="28" t="inlineStr">
@@ -2017,17 +2020,17 @@
       </c>
       <c r="B31" s="28" t="inlineStr">
         <is>
-          <t>Air gas cylinder (drive air)</t>
+          <t>N2 gas cylinder</t>
         </is>
       </c>
       <c r="C31" s="28" t="inlineStr">
         <is>
-          <t>UN1002 Dry Grade</t>
+          <t>UN1066 Ultra High Purity</t>
         </is>
       </c>
       <c r="D31" s="28" t="inlineStr">
         <is>
-          <t>Drives booster pump only — never enters vessel</t>
+          <t>Alternate experiment gas — Metro Welding Supply, Detroit MI</t>
         </is>
       </c>
       <c r="E31" s="28" t="inlineStr">
@@ -2054,114 +2057,202 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="29" t="inlineStr">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>9. Already Owned</t>
+        </is>
+      </c>
+      <c r="B32" s="28" t="inlineStr">
+        <is>
+          <t>Ar gas cylinder</t>
+        </is>
+      </c>
+      <c r="C32" s="28" t="inlineStr">
+        <is>
+          <t>UN1006 Prepurified</t>
+        </is>
+      </c>
+      <c r="D32" s="28" t="inlineStr">
+        <is>
+          <t>Alternate experiment gas — Metro Welding Supply, Detroit MI</t>
+        </is>
+      </c>
+      <c r="E32" s="28" t="inlineStr">
+        <is>
+          <t>No purchase needed (existing supply)</t>
+        </is>
+      </c>
+      <c r="F32" s="28" t="inlineStr">
+        <is>
+          <t>N/A — already owned</t>
+        </is>
+      </c>
+      <c r="G32" s="28" t="inlineStr"/>
+      <c r="H32" s="28" t="inlineStr"/>
+      <c r="I32" s="28" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="J32" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>9. Already Owned</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="inlineStr">
+        <is>
+          <t>Air gas cylinder (drive air)</t>
+        </is>
+      </c>
+      <c r="C33" s="28" t="inlineStr">
+        <is>
+          <t>UN1002 Dry Grade</t>
+        </is>
+      </c>
+      <c r="D33" s="28" t="inlineStr">
+        <is>
+          <t>Drives booster pump only — never enters vessel</t>
+        </is>
+      </c>
+      <c r="E33" s="28" t="inlineStr">
+        <is>
+          <t>No purchase needed (existing supply)</t>
+        </is>
+      </c>
+      <c r="F33" s="28" t="inlineStr">
+        <is>
+          <t>N/A — already owned</t>
+        </is>
+      </c>
+      <c r="G33" s="28" t="inlineStr"/>
+      <c r="H33" s="28" t="inlineStr"/>
+      <c r="I33" s="28" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="J33" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="29" t="inlineStr">
         <is>
           <t>10. Optional: Windowed Vessel</t>
         </is>
       </c>
-      <c r="B32" s="29" t="inlineStr">
+      <c r="B34" s="29" t="inlineStr">
         <is>
           <t>Windowed pressure vessel (sapphire window)</t>
         </is>
       </c>
-      <c r="C32" s="29" t="inlineStr">
+      <c r="C34" s="29" t="inlineStr">
         <is>
           <t>EZE-Seal series</t>
         </is>
       </c>
-      <c r="D32" s="29" t="inlineStr">
+      <c r="D34" s="29" t="inlineStr">
         <is>
           <t>Autoclave Engineers (Parker) windowed reactor for flow visualization</t>
         </is>
       </c>
-      <c r="E32" s="29" t="inlineStr">
+      <c r="E34" s="29" t="inlineStr">
         <is>
           <t>Sapphire window, up to 60 MPa</t>
         </is>
       </c>
-      <c r="F32" s="29" t="inlineStr">
+      <c r="F34" s="29" t="inlineStr">
         <is>
           <t>Autoclave Engineers (Parker)</t>
         </is>
       </c>
-      <c r="G32" s="29" t="n">
+      <c r="G34" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="30" t="n">
+      <c r="H34" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="I32" s="30" t="n">
+      <c r="I34" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="J32" s="31" t="inlineStr">
-        <is>
-          <t>Open product page</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="29" t="inlineStr">
+      <c r="J34" s="31" t="inlineStr">
+        <is>
+          <t>EZE-Seal Windowed Reactor</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="inlineStr">
         <is>
           <t>10. Optional: Windowed Vessel</t>
         </is>
       </c>
-      <c r="B33" s="29" t="inlineStr">
+      <c r="B35" s="29" t="inlineStr">
         <is>
           <t>Windowed pressure vessel (alternate)</t>
         </is>
       </c>
-      <c r="C33" s="29" t="inlineStr">
+      <c r="C35" s="29" t="inlineStr">
         <is>
           <t>Sitec 100-600 mL</t>
         </is>
       </c>
-      <c r="D33" s="29" t="inlineStr">
+      <c r="D35" s="29" t="inlineStr">
         <is>
           <t>Sitec Reactor Technology windowed reactor, sapphire/borosilicate</t>
         </is>
       </c>
-      <c r="E33" s="29" t="inlineStr">
+      <c r="E35" s="29" t="inlineStr">
         <is>
           <t>Up to 100 MPa, 100-600 mL volume</t>
         </is>
       </c>
-      <c r="F33" s="29" t="inlineStr">
+      <c r="F35" s="29" t="inlineStr">
         <is>
           <t>Sitec Reactor Technology</t>
         </is>
       </c>
-      <c r="G33" s="29" t="n">
+      <c r="G35" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="30" t="n">
+      <c r="H35" s="30" t="n">
         <v>4500</v>
       </c>
-      <c r="I33" s="30" t="n">
+      <c r="I35" s="30" t="n">
         <v>4500</v>
       </c>
-      <c r="J33" s="31" t="inlineStr">
-        <is>
-          <t>Open product page</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="32" t="inlineStr"/>
-      <c r="B34" s="32" t="inlineStr"/>
-      <c r="C34" s="32" t="inlineStr"/>
-      <c r="D34" s="32" t="inlineStr"/>
-      <c r="E34" s="32" t="inlineStr"/>
-      <c r="F34" s="32" t="inlineStr"/>
-      <c r="G34" s="32" t="inlineStr"/>
-      <c r="H34" s="32" t="inlineStr">
+      <c r="J35" s="31" t="inlineStr">
+        <is>
+          <t>Sitec Windowed Reactor</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="32" t="inlineStr"/>
+      <c r="B36" s="32" t="inlineStr"/>
+      <c r="C36" s="32" t="inlineStr"/>
+      <c r="D36" s="32" t="inlineStr"/>
+      <c r="E36" s="32" t="inlineStr"/>
+      <c r="F36" s="32" t="inlineStr"/>
+      <c r="G36" s="32" t="inlineStr"/>
+      <c r="H36" s="32" t="inlineStr">
         <is>
           <t>TOTAL (required, excl. optional window vessel)</t>
         </is>
       </c>
-      <c r="I34" s="33" t="n">
-        <v>3240</v>
-      </c>
-      <c r="J34" s="32" t="inlineStr"/>
+      <c r="I36" s="33" t="n">
+        <v>2312.29</v>
+      </c>
+      <c r="J36" s="32" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2186,9 +2277,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2200,7 +2290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A44"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="115" customWidth="1" min="1" max="1"/>
@@ -2219,14 +2309,14 @@
     <row r="3">
       <c r="A3" s="35" t="inlineStr">
         <is>
-          <t>LINKS: All links in this BOM are direct product page URLs (not search pages).</t>
+          <t>LINKS: All links in this BOM are direct product page URLs named by part number.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="35" t="inlineStr">
         <is>
-          <t>A few items use search URLs where no single confirmed direct product page exists.</t>
+          <t>A few items (shaft coupler, Grainger items) use search URLs where no single confirmed direct page exists.</t>
         </is>
       </c>
     </row>
@@ -2236,107 +2326,107 @@
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>CRITICAL SAFETY CORRECTIONS (July 2026 audit):</t>
+          <t>EXISTING HARDWARE DISCOVERED — DO NOT RE-BUY:</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr"/>
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HiP valve on booster outlet → covers supply shutoff (was BV-1). Saves ~$407.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>1. RELIEF VALVE — Part changed from SS-RL3S4 to SS-4R3A</t>
+          <t xml:space="preserve">  Swagelok SS-3NRM4 on vessel outlet → covers vent isolation (was BV-3). Saves ~$407.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   SS-RL3S4 is Swagelok's LOW-PRESSURE series — maximum set pressure 225 PSI.</t>
+          <t xml:space="preserve">  Duro United 0-5000 PSI gauge on vessel → covers visual reference (was K4201). Saves ~$100.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Your system operates at 4,061 PSI (28 MPa). SS-RL3S4 would blow open at 225 PSI</t>
+          <t xml:space="preserve">  Result: only 1 ball valve needed (SS-83KS4 × 1 for vessel inlet isolation).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   and never hold pressure. The correct part is SS-4R3A (HIGH-pressure, up to 6,000 PSI).</t>
-        </is>
-      </c>
+      <c r="A11" s="35" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Set pressure must be specified at ordering: recommend 4,350 PSI (30 MPa).</t>
+          <t>⚠ SS-3NRM4 MUST remain OPEN during automated operation.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr"/>
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  The solenoid valve (SV-1) controls automated venting. Closing the SS-3NRM4 blocks it.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>2. STAINLESS TUBING — Must be 0.065" wall, NOT 0.035" wall</t>
+          <t xml:space="preserve">  Only close SS-3NRM4 for maintenance or emergency manual isolation.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Amazon FITOK B0BB1122VJ (1/4" OD x 0.035" wall) is rated ~3,200 PSI — insufficient</t>
-        </is>
-      </c>
+      <c r="A15" s="35" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   for 4,061 PSI operation with adequate safety margin. The 0.065" wall version</t>
+          <t>CRITICAL SAFETY CORRECTIONS (July 2026 audit):</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   (SS-T4-S-065-20) is rated ~7,400 PSI and is the correct choice. Order from McMaster-Carr.</t>
-        </is>
-      </c>
+      <c r="A17" s="35" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr"/>
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>1. RELIEF VALVE — Part changed from SS-RL3S4 to SS-4R3A</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>3. RELAY MODULE — Must accept 3.3V RPi GPIO trigger</t>
+          <t xml:space="preserve">   SS-RL3S4 is Swagelok's LOW-PRESSURE series — maximum set pressure 225 PSI.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   GAEYAELE B07DYLKH74 requires 24VDC trigger (PLC-grade). Raspberry Pi GPIO 18</t>
+          <t xml:space="preserve">   Your system operates at 4,061 PSI. SS-RL3S4 would blow open at 225 PSI.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   outputs 3.3V — this relay will not fire. Use an optocoupler-isolated relay module</t>
+          <t xml:space="preserve">   Correct part: SS-4R3A (HIGH-pressure, up to 6,000 PSI).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   with 5V coil that accepts 3.3V logic trigger (common Arduino/RPi relay boards).</t>
+          <t xml:space="preserve">   Set pressure must be specified at ordering: recommend 4,350 PSI (30 MPa).</t>
         </is>
       </c>
     </row>
@@ -2346,69 +2436,69 @@
     <row r="24">
       <c r="A24" s="35" t="inlineStr">
         <is>
-          <t>4. PRESSURE TRANSDUCER — Order item 5DEK9 (4-20 mA), NOT K4708 (1-5V DC)</t>
+          <t>2. STAINLESS TUBING — Must be 0.065" wall seamless annealed</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   K4708 has the wrong output type for the 250-ohm shunt wiring designed into the system.</t>
+          <t xml:space="preserve">   Grainger 5LVR1: seamless annealed, 0.065" wall, rated 8,125 PSI. Buy 3 × 6ft = 18ft.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="35" t="inlineStr"/>
+      <c r="A26" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Amazon FITOK B0BB1122VJ (0.035" wall, ~3,200 PSI) is NOT safe for this system.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="35" t="inlineStr">
         <is>
-          <t>5. VENT SOLENOID VALVE — Was missing from original BOM, now added</t>
+          <t xml:space="preserve">   Must be SEAMLESS (not welded) for Swagelok compression fittings to seal correctly.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Must be rated &gt;= 6,000 PSI. Standard solenoids (150-300 PSI) will rupture at 28 MPa.</t>
-        </is>
-      </c>
+      <c r="A28" s="35" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="35" t="inlineStr"/>
+      <c r="A29" s="35" t="inlineStr">
+        <is>
+          <t>3. RELAY MODULE — Must accept 3.3V RPi GPIO trigger</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="35" t="inlineStr">
         <is>
-          <t>Why exact Swagelok part numbers matter:</t>
+          <t xml:space="preserve">   AEDIKO B095YD3732: optocoupler isolated, 1-channel, 5V coil, 3.3V-compatible input.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="35" t="inlineStr">
         <is>
-          <t>- SS-CHS4-5 (check valve): 6,000 PSI. SS-4C looks similar but is only 3,000 PSI.</t>
+          <t xml:space="preserve">   GAEYAELE B07DYLKH74 requires 24VDC trigger (PLC-grade) — will not work with RPi.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="35" t="inlineStr">
-        <is>
-          <t>- SS-83KS4 (ball valve): 6,000 PSI. SS-43GS4 looks similar but is only 3,000 PSI.</t>
-        </is>
-      </c>
+      <c r="A32" s="35" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="35" t="inlineStr">
         <is>
-          <t>- All SS-400 fittings: 5,100 PSI rated, matched to 1/4" tube OD throughout.</t>
+          <t>4. PRESSURE TRANSDUCER — Order item 5DEK9 (4-20 mA), NOT K4708 (1-5V DC)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="35" t="inlineStr">
         <is>
-          <t>- SS-1RS4 needle valve: 5,000 PSI gives ~23% margin above 4,061 PSI operating pressure.</t>
+          <t xml:space="preserve">   K4708 has the wrong output type for the 250-ohm shunt wiring in this system.</t>
         </is>
       </c>
     </row>
@@ -2418,14 +2508,14 @@
     <row r="36">
       <c r="A36" s="35" t="inlineStr">
         <is>
-          <t>CanaKit note: B07V5JTMV9 starter kit includes a 32GB SD card. Do not also buy</t>
+          <t>5. VENT SOLENOID VALVE — Was missing from original BOM, now added</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="35" t="inlineStr">
         <is>
-          <t>the separate microSD card listed in section 8 — it would be a duplicate purchase.</t>
+          <t xml:space="preserve">   Must be rated &gt;= 6,000 PSI. Standard solenoids (150-300 PSI) will rupture at 28 MPa.</t>
         </is>
       </c>
     </row>
@@ -2435,42 +2525,80 @@
     <row r="39">
       <c r="A39" s="35" t="inlineStr">
         <is>
-          <t>Recommended buying order:</t>
+          <t>Why exact Swagelok part numbers matter:</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="35" t="inlineStr">
         <is>
-          <t>1. Confirm tube/thread size compatibility with your PARR vessel fittings first.</t>
+          <t>- SS-CHS4-5 (check valve): 6,000 PSI. SS-4C looks similar but is only 3,000 PSI.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="35" t="inlineStr">
         <is>
-          <t>2. Order Swagelok parts from an authorized distributor (warranty/traceability on 28 MPa system).</t>
+          <t>- SS-83KS4 (ball valve): 6,000 PSI. SS-43GS4 looks similar but is only 3,000 PSI.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="35" t="inlineStr">
         <is>
-          <t>3. Specify set pressure 4,350 PSI when ordering the SS-4R3A relief valve.</t>
+          <t>- All SS-400 fittings: 5,100 PSI rated, matched to 1/4" tube OD throughout.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="35" t="inlineStr">
         <is>
-          <t>4. McMaster-Carr ships fastest for tubing; Grainger for PSU, gauge, and PTFE tape.</t>
+          <t>- SS-1RS4 needle valve: 5,000 PSI @ 100°F — confirmed suitable for 4,061 PSI at 60°C.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="35" t="inlineStr">
-        <is>
-          <t>5. Electronics (RPi, ADC, stepper driver) — any reputable Amazon seller is fine.</t>
+      <c r="A44" s="35" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="35" t="inlineStr">
+        <is>
+          <t>Recommended buying order:</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="35" t="inlineStr">
+        <is>
+          <t>1. Confirm tube/thread size compatibility with PARR vessel fittings first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="35" t="inlineStr">
+        <is>
+          <t>2. Order Swagelok parts from an authorized distributor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="35" t="inlineStr">
+        <is>
+          <t>3. Specify set pressure 4,350 PSI when ordering the SS-4R3A relief valve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="35" t="inlineStr">
+        <is>
+          <t>4. Grainger for tubing (5LVR1) and PSU (33NT20). Amazon for electronics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="35" t="inlineStr">
+        <is>
+          <t>5. Source high-pressure solenoid valve from Parker or Asco distributor.</t>
         </is>
       </c>
     </row>

--- a/scCO2_Full_Bill_of_Materials.xlsx
+++ b/scCO2_Full_Bill_of_Materials.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,11 +47,6 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
@@ -64,7 +59,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -125,24 +120,6 @@
         <bgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6D9E8"/>
-        <bgColor rgb="00D6D9E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ECEFF1"/>
-        <bgColor rgb="00ECEFF1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F3E5F5"/>
-        <bgColor rgb="00F3E5F5"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -170,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -247,24 +224,10 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -632,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -780,10 +743,10 @@
         <v>1</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -826,10 +789,10 @@
         <v>1</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
@@ -840,7 +803,7 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>3. Manual Ball Valves</t>
+          <t>3. Manual Ball Valve</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -856,8 +819,8 @@
       <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Swagelok 83 series ball valve, 1/4" tube fitting, PCTFE seats, CO2 compatible
-Only 1 needed — HiP valve on booster outlet covers supply shutoff position;
-SS-3NRM4 already on vessel outlet covers vent isolation position</t>
+Only 1 needed — HiP valve on booster covers supply shutoff;
+SS-3NRM4 already on vessel outlet covers vent isolation</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -904,15 +867,15 @@
       <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Seamless 316SS tubing, 6 ft length — ASTM A213 + A269, annealed
-Buy 3 pieces (18 ft total) for adequate spare — system needs ~10 ft
-⚠ Must be seamless annealed (NOT welded) for Swagelok compression fittings
-⚠ Amazon FITOK B0BB1122VJ is only 0.035" wall (~3,200 PSI) — NOT safe</t>
+Buy 3 pieces (18 ft total); system needs ~10 ft
+Must be seamless annealed (NOT welded) for Swagelok compression fittings
+Amazon FITOK B0BB1122VJ is only 0.035" wall (~3,200 PSI) — NOT safe</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
           <t>316SS seamless annealed, 1/4" OD × 0.065" wall, 6 ft per piece
-Rated 8,125 PSI @ 72°F — 2× safety margin over 4,061 PSI operating pressure</t>
+Rated 8,125 PSI @ 72°F — 2x safety margin over 4,061 PSI operating pressure</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -1122,7 +1085,7 @@
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>6. Relief Valve</t>
+          <t>6. Relief Valve &amp; Vent</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
@@ -1138,8 +1101,8 @@
       <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Swagelok HIGH-PRESSURE proportional relief valve, 1/4" tube compression
-⚠ MUST specify set pressure ~4,350 PSI (30 MPa) when ordering from distributor
-⚠ SS-RL3S4 (previously listed) is LOW-PRESSURE only (max 225 PSI) — DANGEROUS for this system</t>
+Specify set pressure ~4,350 PSI (30 MPa) when ordering from distributor
+SS-RL3S4 is LOW-PRESSURE only (max 225 PSI) — DANGEROUS for this system</t>
         </is>
       </c>
       <c r="E11" s="17" t="inlineStr">
@@ -1171,7 +1134,7 @@
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>6. Relief Valve</t>
+          <t>6. Relief Valve &amp; Vent</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
@@ -1188,8 +1151,7 @@
         <is>
           <t>Normally-closed 24VDC solenoid valve, 1/4" tube or NPT, HIGH-pressure rated
 Driven by RPi GPIO 18 via relay — opens automatically during DEPRESSURIZE state
-⚠ MUST be rated ≥ 6,000 PSI — standard solenoids (150-300 PSI) will fail catastrophically
-⚠ This part was MISSING from the original BOM</t>
+MUST be rated &gt;= 6,000 PSI — standard solenoids (150-300 PSI) will fail catastrophically</t>
         </is>
       </c>
       <c r="E12" s="17" t="inlineStr">
@@ -1221,7 +1183,7 @@
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>6. Relief Valve</t>
+          <t>6. Relief Valve &amp; Vent</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
@@ -1282,15 +1244,14 @@
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Ashcroft G2, 0-5000 PSI, 4-20 mA output, nylon housing, 316SS wetted parts, IP67
+          <t>Ashcroft G2, 0-5000 PSI, 4-20 mA output, 316SS wetted parts, IP67
 Grainger item 5DEK9 — Mfr model G17M0242F25000#
-⚠ Do NOT order K4708 — that is the 1-5V DC output version, incompatible with 4-20mA wiring</t>
+Do NOT order K4708 — that is the 1-5V DC output version, wrong for 4-20mA wiring</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>4-20 mA → 1-5 V via 250 ohm shunt resistor into ADS1115 A0
-Nylon housing is fine for lab use; 316SS diaphragm is the CO2-wetted part</t>
+          <t>4-20 mA → 1-5 V via 250 ohm shunt resistor into ADS1115 A0</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -1302,10 +1263,10 @@
         <v>1</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="J14" s="22" t="inlineStr">
         <is>
@@ -1331,8 +1292,8 @@
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>CanaKit Starter Pro Kit: RPi4 4GB + case + 3.5A power supply + 32GB SD card + heatsinks
-SD card is INCLUDED in this kit — do NOT buy the separate microSD card</t>
+          <t>CanaKit Starter Pro Kit: RPi4 4GB + case + 3.5A PSU + 32GB SD card + heatsinks
+SD card is INCLUDED — do NOT buy separate microSD</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -1349,10 +1310,10 @@
         <v>1</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>100</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>100</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="J15" s="25" t="inlineStr">
         <is>
@@ -1378,7 +1339,8 @@
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>Reads pressure transducer (A0) and temperature sensor (A1)</t>
+          <t>Reads pressure transducer (A0) and temperature sensor (A1) via I2C
+Qoroos 3-pack — only 1 needed, extras are spares</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -1395,10 +1357,10 @@
         <v>1</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>10</v>
+        <v>12.99</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>10</v>
+        <v>12.99</v>
       </c>
       <c r="J16" s="25" t="inlineStr">
         <is>
@@ -1429,7 +1391,7 @@
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
-          <t>200 steps/rev, bipolar, NEMA 17 frame</t>
+          <t>200 steps/rev, bipolar, NEMA 17 frame, 5mm shaft</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -1441,10 +1403,10 @@
         <v>1</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>15</v>
+        <v>15.99</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>15</v>
+        <v>15.99</v>
       </c>
       <c r="J17" s="25" t="inlineStr">
         <is>
@@ -1487,10 +1449,10 @@
         <v>1</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>8</v>
+        <v>7.99</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>8</v>
+        <v>7.99</v>
       </c>
       <c r="J18" s="25" t="inlineStr">
         <is>
@@ -1517,8 +1479,8 @@
       <c r="D19" s="23" t="inlineStr">
         <is>
           <t>AEDIKO 1-channel optocoupler-isolated relay module
-RPi GPIO 18 (3.3V) → relay IN → switches 24VDC to solenoid
-⚠ GAEYAELE B07DYLKH74 (prev BOM) requires 24VDC trigger — NOT compatible with RPi 3.3V GPIO</t>
+RPi GPIO 18 (3.3V) triggers relay → switches 24VDC to solenoid
+GAEYAELE B07DYLKH74 requires 24VDC trigger — NOT compatible with RPi 3.3V GPIO</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -1535,10 +1497,10 @@
         <v>1</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="J19" s="25" t="inlineStr">
         <is>
@@ -1564,13 +1526,12 @@
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>Male-to-female and male-to-male jumper wires for GPIO connections
-RPi GPIO → ADS1115 (4 wires), A4988 (3 wires), relay module (3 wires)</t>
+          <t>Male-to-female and male-to-male jumper wires for GPIO connections</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>120-piece assorted kit: male-to-male + male-to-female</t>
+          <t>120-piece assorted: male-to-male + male-to-female</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
@@ -1582,10 +1543,10 @@
         <v>1</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>7</v>
+        <v>6.99</v>
       </c>
       <c r="I20" s="24" t="n">
-        <v>7</v>
+        <v>6.99</v>
       </c>
       <c r="J20" s="25" t="inlineStr">
         <is>
@@ -1601,22 +1562,22 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>DIN rail relay, 24VDC coil</t>
+          <t>DIN rail power supply, 24VDC 50W</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>4WAU2</t>
+          <t>33NT20</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>DIN-rail mounted relay for panel-style wiring of solenoid circuit (optional for bench setup)</t>
+          <t>Dayton DIN rail PSU — powers relay, solenoid, and sensor circuits</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t>24VDC coil</t>
+          <t>24VDC, 50W output</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -1628,631 +1589,34 @@
         <v>1</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="I21" s="24" t="n">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="J21" s="25" t="inlineStr">
         <is>
-          <t>4WAU2 DIN Rail Relay</t>
+          <t>33NT20 DIN Rail PSU</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="23" t="inlineStr">
-        <is>
-          <t>8. Electronics &amp; Control</t>
-        </is>
-      </c>
-      <c r="B22" s="23" t="inlineStr">
-        <is>
-          <t>DIN rail power supply, 24VDC 50W</t>
-        </is>
-      </c>
-      <c r="C22" s="23" t="inlineStr">
-        <is>
-          <t>33NT20</t>
-        </is>
-      </c>
-      <c r="D22" s="23" t="inlineStr">
-        <is>
-          <t>Dayton DIN rail PSU — powers relay, solenoid, and sensor circuits</t>
-        </is>
-      </c>
-      <c r="E22" s="23" t="inlineStr">
-        <is>
-          <t>24VDC, 50W output</t>
-        </is>
-      </c>
-      <c r="F22" s="23" t="inlineStr">
-        <is>
-          <t>Grainger</t>
-        </is>
-      </c>
-      <c r="G22" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="24" t="n">
-        <v>55</v>
-      </c>
-      <c r="I22" s="24" t="n">
-        <v>55</v>
-      </c>
-      <c r="J22" s="25" t="inlineStr">
-        <is>
-          <t>33NT20 DIN Rail PSU</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="26" t="inlineStr"/>
-      <c r="B23" s="26" t="inlineStr"/>
-      <c r="C23" s="26" t="inlineStr"/>
-      <c r="D23" s="26" t="inlineStr"/>
-      <c r="E23" s="26" t="inlineStr"/>
-      <c r="F23" s="26" t="inlineStr"/>
-      <c r="G23" s="26" t="inlineStr"/>
-      <c r="H23" s="26" t="inlineStr">
-        <is>
-          <t>SUBTOTAL (to buy)</t>
-        </is>
-      </c>
-      <c r="I23" s="27" t="n">
-        <v>2312.29</v>
-      </c>
-      <c r="J23" s="26" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>9. Already Owned</t>
-        </is>
-      </c>
-      <c r="B24" s="28" t="inlineStr">
-        <is>
-          <t>Pressure vessel</t>
-        </is>
-      </c>
-      <c r="C24" s="28" t="inlineStr">
-        <is>
-          <t>PARR 2302HC</t>
-        </is>
-      </c>
-      <c r="D24" s="28" t="inlineStr">
-        <is>
-          <t>316SS pressure vessel, S/N 4540-1803-78845A, 1 L volume</t>
-        </is>
-      </c>
-      <c r="E24" s="28" t="inlineStr">
-        <is>
-          <t>MAWP 5,000 PSI (34.47 MPa) @ 350°C — no purchase needed</t>
-        </is>
-      </c>
-      <c r="F24" s="28" t="inlineStr">
-        <is>
-          <t>N/A — already owned</t>
-        </is>
-      </c>
-      <c r="G24" s="28" t="inlineStr"/>
-      <c r="H24" s="28" t="inlineStr"/>
-      <c r="I24" s="28" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="J24" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>9. Already Owned</t>
-        </is>
-      </c>
-      <c r="B25" s="28" t="inlineStr">
-        <is>
-          <t>Gas booster pump</t>
-        </is>
-      </c>
-      <c r="C25" s="28" t="inlineStr">
-        <is>
-          <t>HII 5G-TD-28/150-CO2</t>
-        </is>
-      </c>
-      <c r="D25" s="28" t="inlineStr">
-        <is>
-          <t>Air-driven, twin-drive CO2 service booster, S/N 1205101</t>
-        </is>
-      </c>
-      <c r="E25" s="28" t="inlineStr">
-        <is>
-          <t>Max outlet 25,000 PSIG (172 MPa) — no purchase needed</t>
-        </is>
-      </c>
-      <c r="F25" s="28" t="inlineStr">
-        <is>
-          <t>N/A — already owned</t>
-        </is>
-      </c>
-      <c r="G25" s="28" t="inlineStr"/>
-      <c r="H25" s="28" t="inlineStr"/>
-      <c r="I25" s="28" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="J25" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="28" t="inlineStr">
-        <is>
-          <t>9. Already Owned</t>
-        </is>
-      </c>
-      <c r="B26" s="28" t="inlineStr">
-        <is>
-          <t>HiP valve on booster outlet</t>
-        </is>
-      </c>
-      <c r="C26" s="28" t="inlineStr">
-        <is>
-          <t>High Pressure Equipment valve</t>
-        </is>
-      </c>
-      <c r="D26" s="28" t="inlineStr">
-        <is>
-          <t>Manual shutoff valve already installed on booster HP outlet — covers BV-1 position</t>
-        </is>
-      </c>
-      <c r="E26" s="28" t="inlineStr">
-        <is>
-          <t>No purchase needed — saves ~$407 vs buying SS-83KS4 here</t>
-        </is>
-      </c>
-      <c r="F26" s="28" t="inlineStr">
-        <is>
-          <t>N/A — already owned</t>
-        </is>
-      </c>
-      <c r="G26" s="28" t="inlineStr"/>
-      <c r="H26" s="28" t="inlineStr"/>
-      <c r="I26" s="28" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="J26" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="28" t="inlineStr">
-        <is>
-          <t>9. Already Owned</t>
-        </is>
-      </c>
-      <c r="B27" s="28" t="inlineStr">
-        <is>
-          <t>SS-3NRM4 needle valve on vessel outlet</t>
-        </is>
-      </c>
-      <c r="C27" s="28" t="inlineStr">
-        <is>
-          <t>Swagelok SS-3NRM4</t>
-        </is>
-      </c>
-      <c r="D27" s="28" t="inlineStr">
-        <is>
-          <t>Manual needle valve already installed on vessel outlet — covers vent isolation position
-⚠ Must remain OPEN during automated operation — solenoid SV-1 controls automated venting</t>
-        </is>
-      </c>
-      <c r="E27" s="28" t="inlineStr">
-        <is>
-          <t>8,000 PSI rated — no purchase needed — saves ~$407 vs buying SS-83KS4 here</t>
-        </is>
-      </c>
-      <c r="F27" s="28" t="inlineStr">
-        <is>
-          <t>N/A — already owned</t>
-        </is>
-      </c>
-      <c r="G27" s="28" t="inlineStr"/>
-      <c r="H27" s="28" t="inlineStr"/>
-      <c r="I27" s="28" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="J27" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="28" t="inlineStr">
-        <is>
-          <t>9. Already Owned</t>
-        </is>
-      </c>
-      <c r="B28" s="28" t="inlineStr">
-        <is>
-          <t>Pressure gauge on vessel</t>
-        </is>
-      </c>
-      <c r="C28" s="28" t="inlineStr">
-        <is>
-          <t>Duro United 0-5000 PSI</t>
-        </is>
-      </c>
-      <c r="D28" s="28" t="inlineStr">
-        <is>
-          <t>Mechanical pressure gauge already installed on PARR vessel port</t>
-        </is>
-      </c>
-      <c r="E28" s="28" t="inlineStr">
-        <is>
-          <t>No purchase needed — saves ~$100 vs K4201</t>
-        </is>
-      </c>
-      <c r="F28" s="28" t="inlineStr">
-        <is>
-          <t>N/A — already owned</t>
-        </is>
-      </c>
-      <c r="G28" s="28" t="inlineStr"/>
-      <c r="H28" s="28" t="inlineStr"/>
-      <c r="I28" s="28" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="J28" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="28" t="inlineStr">
-        <is>
-          <t>9. Already Owned</t>
-        </is>
-      </c>
-      <c r="B29" s="28" t="inlineStr">
-        <is>
-          <t>Temperature controller</t>
-        </is>
-      </c>
-      <c r="C29" s="28" t="inlineStr">
-        <is>
-          <t>INKBIRD</t>
-        </is>
-      </c>
-      <c r="D29" s="28" t="inlineStr">
-        <is>
-          <t>60C setpoint temperature controller</t>
-        </is>
-      </c>
-      <c r="E29" s="28" t="inlineStr">
-        <is>
-          <t>±0.01°C settled stability — no purchase needed</t>
-        </is>
-      </c>
-      <c r="F29" s="28" t="inlineStr">
-        <is>
-          <t>N/A — already owned</t>
-        </is>
-      </c>
-      <c r="G29" s="28" t="inlineStr"/>
-      <c r="H29" s="28" t="inlineStr"/>
-      <c r="I29" s="28" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="J29" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="28" t="inlineStr">
-        <is>
-          <t>9. Already Owned</t>
-        </is>
-      </c>
-      <c r="B30" s="28" t="inlineStr">
-        <is>
-          <t>CO2 gas cylinder</t>
-        </is>
-      </c>
-      <c r="C30" s="28" t="inlineStr">
-        <is>
-          <t>UN1013 Bone Dry</t>
-        </is>
-      </c>
-      <c r="D30" s="28" t="inlineStr">
-        <is>
-          <t>Primary process gas — Metro Welding Supply, Detroit MI</t>
-        </is>
-      </c>
-      <c r="E30" s="28" t="inlineStr">
-        <is>
-          <t>No purchase needed (existing supply)</t>
-        </is>
-      </c>
-      <c r="F30" s="28" t="inlineStr">
-        <is>
-          <t>N/A — already owned</t>
-        </is>
-      </c>
-      <c r="G30" s="28" t="inlineStr"/>
-      <c r="H30" s="28" t="inlineStr"/>
-      <c r="I30" s="28" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="J30" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="28" t="inlineStr">
-        <is>
-          <t>9. Already Owned</t>
-        </is>
-      </c>
-      <c r="B31" s="28" t="inlineStr">
-        <is>
-          <t>N2 gas cylinder</t>
-        </is>
-      </c>
-      <c r="C31" s="28" t="inlineStr">
-        <is>
-          <t>UN1066 Ultra High Purity</t>
-        </is>
-      </c>
-      <c r="D31" s="28" t="inlineStr">
-        <is>
-          <t>Alternate experiment gas — Metro Welding Supply, Detroit MI</t>
-        </is>
-      </c>
-      <c r="E31" s="28" t="inlineStr">
-        <is>
-          <t>No purchase needed (existing supply)</t>
-        </is>
-      </c>
-      <c r="F31" s="28" t="inlineStr">
-        <is>
-          <t>N/A — already owned</t>
-        </is>
-      </c>
-      <c r="G31" s="28" t="inlineStr"/>
-      <c r="H31" s="28" t="inlineStr"/>
-      <c r="I31" s="28" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="J31" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="28" t="inlineStr">
-        <is>
-          <t>9. Already Owned</t>
-        </is>
-      </c>
-      <c r="B32" s="28" t="inlineStr">
-        <is>
-          <t>Ar gas cylinder</t>
-        </is>
-      </c>
-      <c r="C32" s="28" t="inlineStr">
-        <is>
-          <t>UN1006 Prepurified</t>
-        </is>
-      </c>
-      <c r="D32" s="28" t="inlineStr">
-        <is>
-          <t>Alternate experiment gas — Metro Welding Supply, Detroit MI</t>
-        </is>
-      </c>
-      <c r="E32" s="28" t="inlineStr">
-        <is>
-          <t>No purchase needed (existing supply)</t>
-        </is>
-      </c>
-      <c r="F32" s="28" t="inlineStr">
-        <is>
-          <t>N/A — already owned</t>
-        </is>
-      </c>
-      <c r="G32" s="28" t="inlineStr"/>
-      <c r="H32" s="28" t="inlineStr"/>
-      <c r="I32" s="28" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="J32" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="28" t="inlineStr">
-        <is>
-          <t>9. Already Owned</t>
-        </is>
-      </c>
-      <c r="B33" s="28" t="inlineStr">
-        <is>
-          <t>Air gas cylinder (drive air)</t>
-        </is>
-      </c>
-      <c r="C33" s="28" t="inlineStr">
-        <is>
-          <t>UN1002 Dry Grade</t>
-        </is>
-      </c>
-      <c r="D33" s="28" t="inlineStr">
-        <is>
-          <t>Drives booster pump only — never enters vessel</t>
-        </is>
-      </c>
-      <c r="E33" s="28" t="inlineStr">
-        <is>
-          <t>No purchase needed (existing supply)</t>
-        </is>
-      </c>
-      <c r="F33" s="28" t="inlineStr">
-        <is>
-          <t>N/A — already owned</t>
-        </is>
-      </c>
-      <c r="G33" s="28" t="inlineStr"/>
-      <c r="H33" s="28" t="inlineStr"/>
-      <c r="I33" s="28" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="J33" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="29" t="inlineStr">
-        <is>
-          <t>10. Optional: Windowed Vessel</t>
-        </is>
-      </c>
-      <c r="B34" s="29" t="inlineStr">
-        <is>
-          <t>Windowed pressure vessel (sapphire window)</t>
-        </is>
-      </c>
-      <c r="C34" s="29" t="inlineStr">
-        <is>
-          <t>EZE-Seal series</t>
-        </is>
-      </c>
-      <c r="D34" s="29" t="inlineStr">
-        <is>
-          <t>Autoclave Engineers (Parker) windowed reactor for flow visualization</t>
-        </is>
-      </c>
-      <c r="E34" s="29" t="inlineStr">
-        <is>
-          <t>Sapphire window, up to 60 MPa</t>
-        </is>
-      </c>
-      <c r="F34" s="29" t="inlineStr">
-        <is>
-          <t>Autoclave Engineers (Parker)</t>
-        </is>
-      </c>
-      <c r="G34" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="30" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I34" s="30" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J34" s="31" t="inlineStr">
-        <is>
-          <t>EZE-Seal Windowed Reactor</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="29" t="inlineStr">
-        <is>
-          <t>10. Optional: Windowed Vessel</t>
-        </is>
-      </c>
-      <c r="B35" s="29" t="inlineStr">
-        <is>
-          <t>Windowed pressure vessel (alternate)</t>
-        </is>
-      </c>
-      <c r="C35" s="29" t="inlineStr">
-        <is>
-          <t>Sitec 100-600 mL</t>
-        </is>
-      </c>
-      <c r="D35" s="29" t="inlineStr">
-        <is>
-          <t>Sitec Reactor Technology windowed reactor, sapphire/borosilicate</t>
-        </is>
-      </c>
-      <c r="E35" s="29" t="inlineStr">
-        <is>
-          <t>Up to 100 MPa, 100-600 mL volume</t>
-        </is>
-      </c>
-      <c r="F35" s="29" t="inlineStr">
-        <is>
-          <t>Sitec Reactor Technology</t>
-        </is>
-      </c>
-      <c r="G35" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="30" t="n">
-        <v>4500</v>
-      </c>
-      <c r="I35" s="30" t="n">
-        <v>4500</v>
-      </c>
-      <c r="J35" s="31" t="inlineStr">
-        <is>
-          <t>Sitec Windowed Reactor</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="32" t="inlineStr"/>
-      <c r="B36" s="32" t="inlineStr"/>
-      <c r="C36" s="32" t="inlineStr"/>
-      <c r="D36" s="32" t="inlineStr"/>
-      <c r="E36" s="32" t="inlineStr"/>
-      <c r="F36" s="32" t="inlineStr"/>
-      <c r="G36" s="32" t="inlineStr"/>
-      <c r="H36" s="32" t="inlineStr">
-        <is>
-          <t>TOTAL (required, excl. optional window vessel)</t>
-        </is>
-      </c>
-      <c r="I36" s="33" t="n">
-        <v>2312.29</v>
-      </c>
-      <c r="J36" s="32" t="inlineStr"/>
+      <c r="A22" s="26" t="inlineStr"/>
+      <c r="B22" s="26" t="inlineStr"/>
+      <c r="C22" s="26" t="inlineStr"/>
+      <c r="D22" s="26" t="inlineStr"/>
+      <c r="E22" s="26" t="inlineStr"/>
+      <c r="F22" s="26" t="inlineStr"/>
+      <c r="G22" s="26" t="inlineStr"/>
+      <c r="H22" s="26" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="I22" s="27" t="n">
+        <v>2349.219999999998</v>
+      </c>
+      <c r="J22" s="26" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2276,9 +1640,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2290,16 +1651,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A50"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="115" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
-        <is>
-          <t>scCO2 System — Complete BOM Notes &amp; Safety Corrections</t>
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>scCO2 System — Purchase List Notes &amp; Safety Corrections</t>
         </is>
       </c>
     </row>
@@ -2307,298 +1668,211 @@
       <c r="A2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="35" t="inlineStr">
-        <is>
-          <t>LINKS: All links in this BOM are direct product page URLs named by part number.</t>
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>This BOM lists only items to purchase. Already-owned equipment:</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="35" t="inlineStr">
-        <is>
-          <t>A few items (shaft coupler, Grainger items) use search URLs where no single confirmed direct page exists.</t>
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HiP valve on booster outlet — covers supply shutoff position (saves ~$407)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr"/>
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Swagelok SS-3NRM4 on vessel outlet — covers vent isolation (saves ~$407)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
-        <is>
-          <t>EXISTING HARDWARE DISCOVERED — DO NOT RE-BUY:</t>
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Duro United 0-5000 PSI gauge on vessel — visual reference (saves ~$100+)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  HiP valve on booster outlet → covers supply shutoff (was BV-1). Saves ~$407.</t>
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PARR 2302HC vessel, HII 5G-TD booster, INKBIRD temp controller, gas cylinders</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Swagelok SS-3NRM4 on vessel outlet → covers vent isolation (was BV-3). Saves ~$407.</t>
-        </is>
-      </c>
+      <c r="A8" s="29" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Duro United 0-5000 PSI gauge on vessel → covers visual reference (was K4201). Saves ~$100.</t>
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>IMPORTANT: SS-3NRM4 MUST remain OPEN during automated operation.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Result: only 1 ball valve needed (SS-83KS4 × 1 for vessel inlet isolation).</t>
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Solenoid SV-1 controls automated venting. Closing SS-3NRM4 blocks it.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="inlineStr"/>
+      <c r="A11" s="29" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>⚠ SS-3NRM4 MUST remain OPEN during automated operation.</t>
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>CRITICAL SAFETY CORRECTIONS:</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  The solenoid valve (SV-1) controls automated venting. Closing the SS-3NRM4 blocks it.</t>
-        </is>
-      </c>
+      <c r="A13" s="29" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Only close SS-3NRM4 for maintenance or emergency manual isolation.</t>
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>1. RELIEF VALVE — SS-4R3A, not SS-RL3S4</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr"/>
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   SS-RL3S4 max set pressure = 225 PSI. System operates at 4,061 PSI.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="inlineStr">
-        <is>
-          <t>CRITICAL SAFETY CORRECTIONS (July 2026 audit):</t>
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   SS-4R3A is rated 6,000 PSI. Specify set pressure 4,350 PSI when ordering.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="inlineStr"/>
+      <c r="A17" s="29" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
-        <is>
-          <t>1. RELIEF VALVE — Part changed from SS-RL3S4 to SS-4R3A</t>
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>2. TUBING — Grainger 5LVR1 (seamless, 0.065" wall, 8,125 PSI)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SS-RL3S4 is Swagelok's LOW-PRESSURE series — maximum set pressure 225 PSI.</t>
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Amazon FITOK B0BB1122VJ is 0.035" wall (~3,200 PSI) — NOT safe.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Your system operates at 4,061 PSI. SS-RL3S4 would blow open at 225 PSI.</t>
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Must be SEAMLESS (not welded) for Swagelok compression fittings.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Correct part: SS-4R3A (HIGH-pressure, up to 6,000 PSI).</t>
-        </is>
-      </c>
+      <c r="A21" s="29" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Set pressure must be specified at ordering: recommend 4,350 PSI (30 MPa).</t>
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>3. RELAY — AEDIKO B095YD3732 (optocoupler, 3.3V trigger compatible)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="35" t="inlineStr"/>
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   GAEYAELE B07DYLKH74 requires 24VDC trigger — will NOT work with RPi GPIO.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="35" t="inlineStr">
-        <is>
-          <t>2. STAINLESS TUBING — Must be 0.065" wall seamless annealed</t>
-        </is>
-      </c>
+      <c r="A24" s="29" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Grainger 5LVR1: seamless annealed, 0.065" wall, rated 8,125 PSI. Buy 3 × 6ft = 18ft.</t>
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>4. PRESSURE TRANSDUCER — 5DEK9 (4-20 mA output)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Amazon FITOK B0BB1122VJ (0.035" wall, ~3,200 PSI) is NOT safe for this system.</t>
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   K4708 has 1-5V DC output — wrong type for the 250-ohm shunt wiring.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Must be SEAMLESS (not welded) for Swagelok compression fittings to seal correctly.</t>
-        </is>
-      </c>
+      <c r="A27" s="29" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="35" t="inlineStr"/>
+      <c r="A28" s="29" t="inlineStr">
+        <is>
+          <t>5. VENT SOLENOID — Must be rated &gt;= 6,000 PSI</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="35" t="inlineStr">
-        <is>
-          <t>3. RELAY MODULE — Must accept 3.3V RPi GPIO trigger</t>
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Standard solenoids (150-300 PSI) will rupture at 28 MPa operating pressure.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   AEDIKO B095YD3732: optocoupler isolated, 1-channel, 5V coil, 3.3V-compatible input.</t>
-        </is>
-      </c>
+      <c r="A30" s="29" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   GAEYAELE B07DYLKH74 requires 24VDC trigger (PLC-grade) — will not work with RPi.</t>
+      <c r="A31" s="29" t="inlineStr">
+        <is>
+          <t>Why exact Swagelok part numbers matter:</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="35" t="inlineStr"/>
+      <c r="A32" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SS-CHS4-5: 6,000 PSI. SS-4C looks similar but is only 3,000 PSI.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="35" t="inlineStr">
-        <is>
-          <t>4. PRESSURE TRANSDUCER — Order item 5DEK9 (4-20 mA), NOT K4708 (1-5V DC)</t>
+      <c r="A33" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SS-83KS4: 6,000 PSI. SS-43GS4 looks similar but is only 3,000 PSI.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   K4708 has the wrong output type for the 250-ohm shunt wiring in this system.</t>
+      <c r="A34" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SS-1RS4: 5,000 PSI @ 100F — confirmed suitable for 4,061 PSI at 60C.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="35" t="inlineStr"/>
+      <c r="A35" s="29" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="35" t="inlineStr">
-        <is>
-          <t>5. VENT SOLENOID VALVE — Was missing from original BOM, now added</t>
+      <c r="A36" s="29" t="inlineStr">
+        <is>
+          <t>Swagelok and Parker/Asco prices are estimates — get distributor quotes.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Must be rated &gt;= 6,000 PSI. Standard solenoids (150-300 PSI) will rupture at 28 MPa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="35" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="35" t="inlineStr">
-        <is>
-          <t>Why exact Swagelok part numbers matter:</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="35" t="inlineStr">
-        <is>
-          <t>- SS-CHS4-5 (check valve): 6,000 PSI. SS-4C looks similar but is only 3,000 PSI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="35" t="inlineStr">
-        <is>
-          <t>- SS-83KS4 (ball valve): 6,000 PSI. SS-43GS4 looks similar but is only 3,000 PSI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="35" t="inlineStr">
-        <is>
-          <t>- All SS-400 fittings: 5,100 PSI rated, matched to 1/4" tube OD throughout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="35" t="inlineStr">
-        <is>
-          <t>- SS-1RS4 needle valve: 5,000 PSI @ 100°F — confirmed suitable for 4,061 PSI at 60°C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="35" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="35" t="inlineStr">
-        <is>
-          <t>Recommended buying order:</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="35" t="inlineStr">
-        <is>
-          <t>1. Confirm tube/thread size compatibility with PARR vessel fittings first.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="35" t="inlineStr">
-        <is>
-          <t>2. Order Swagelok parts from an authorized distributor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="35" t="inlineStr">
-        <is>
-          <t>3. Specify set pressure 4,350 PSI when ordering the SS-4R3A relief valve.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="35" t="inlineStr">
-        <is>
-          <t>4. Grainger for tubing (5LVR1) and PSU (33NT20). Amazon for electronics.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="35" t="inlineStr">
-        <is>
-          <t>5. Source high-pressure solenoid valve from Parker or Asco distributor.</t>
+      <c r="A37" s="29" t="inlineStr">
+        <is>
+          <t>Amazon and Grainger prices are as of July 2026.</t>
         </is>
       </c>
     </row>
